--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3427,154 +3427,154 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>INFORME</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>FALLIDO</v>
+        <v>Puntos de código</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>comprobaciones</v>
+        <v>Curva de ganancia</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>Suscribirse</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>Cerrar</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>Correo electrónico</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>(opcional)</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>Cancelar</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="397">
@@ -3587,18 +3587,18 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="400">
@@ -3611,535 +3611,631 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>Error:</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>Convertir a XML</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>Convertir a JSON</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>Convertir a ICC</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>ID del perfil</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>Desplazamiento</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>Tamaño</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>Relleno</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>Tipo</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>Array de {type}</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>(Sin contenido)</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>bytes</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>Sin salida de validación</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>El perfil es válido</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>Error de validación crítico</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>Válido</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>Advertencia</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>Error</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>Desconocido</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>Aprobado</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>Fallido</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>Ver en contexto</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>Detalle de validación</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>Activado por</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>Campo</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>Valor actual</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>Requerido: 0</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>Esperado: {value}</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>No válido</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>Cerrar</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>sangría</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>ordenar claves</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3451,791 +3451,951 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>Primarios de color</v>
+        <v>Entorno</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>Características de transferencia</v>
+        <v>Detectando…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>No se pudo detectar el entorno.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Pantalla HDR</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>Rango completo</v>
+        <v>Gamut amplio</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>Rango reducido</v>
+        <v>Ruta de lienzo HDR</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>ninguna</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>sí</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>INFORME</v>
+        <v>no</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>FALLIDO</v>
+        <v>no informado</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>comprobaciones</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Inspeccionar</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Mostrar</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Leer el perfil ICC incrustado: no requiere códec</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>Suscribirse</v>
+        <v>Mostrar los píxeles</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Representar más brillante que el blanco</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Decodificado por profiletool, por tanto independiente del navegador</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>Cerrar</v>
+        <v>Los navegadores no pueden informar cuánto margen HDR tiene una pantalla, solo si existe una ruta HDR.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>Correo electrónico</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>(opcional)</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>Cancelar</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>Suscribirse</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>Cerrar</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>Error:</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>Convertir a XML</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>Convertir a JSON</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>Convertir a ICC</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>ID del perfil</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>Desplazamiento</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>Tamaño</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>Relleno</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>Tipo</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>Array de {type}</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>(Sin contenido)</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>Sin salida de validación</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>El perfil es válido</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>Error de validación crítico</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>Válido</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>Advertencia</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>Error</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>Desconocido</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>Aprobado</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>Fallido</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>Ver en contexto</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>Detalle de validación</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>Activado por</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>Campo</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>Valor actual</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>Requerido: 0</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>Esperado: {value}</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>No válido</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>Cerrar</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>sangría</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>ordenar claves</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3459,943 +3459,975 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>Detectando…</v>
+        <v>Mostrando el respaldo SDR</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>No se pudo detectar el entorno.</v>
+        <v>Perfil HDR en la cadena</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>Pantalla HDR</v>
+        <v>Las transformaciones a través de un perfil HDR usan su AToB0Tag — la representación SDR fijada que exige la cláusula 8.10.6 — porque la cláusula 8.10.1 no le deja etiquetas TRC. El resultado es ese respaldo, no comportamiento HDR.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>Gamut amplio</v>
+        <v>Son perfiles HDR, sin etiquetas TRC, por lo que el gamut se construye a partir del AToB0Tag: la representación SDR fijada que la cláusula 8.10.6 exige a los consumidores sin procesamiento HDR. No es el gamut HDR del perfil, que no puede dibujarse en un PCS acotado.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>Ruta de lienzo HDR</v>
+        <v>Detectando…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>No se pudo detectar el entorno.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>ninguna</v>
+        <v>Pantalla HDR</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>sí</v>
+        <v>Gamut amplio</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>no</v>
+        <v>Ruta de lienzo HDR</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>no informado</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>Formato</v>
+        <v>ninguna</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>Inspeccionar</v>
+        <v>sí</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>Mostrar</v>
+        <v>no</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>no informado</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>Leer el perfil ICC incrustado: no requiere códec</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>Mostrar los píxeles</v>
+        <v>Inspeccionar</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>Representar más brillante que el blanco</v>
+        <v>Mostrar</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>Decodificado por profiletool, por tanto independiente del navegador</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>Los navegadores no pueden informar cuánto margen HDR tiene una pantalla, solo si existe una ruta HDR.</v>
+        <v>Leer el perfil ICC incrustado: no requiere códec</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>Primarios de color</v>
+        <v>Mostrar los píxeles</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>Características de transferencia</v>
+        <v>Representar más brillante que el blanco</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Decodificado por profiletool, por tanto independiente del navegador</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Los navegadores no pueden informar cuánto margen HDR tiene una pantalla, solo si existe una ruta HDR.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>Rango completo</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>Rango reducido</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>INFORME</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>FALLIDO</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>comprobaciones</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>Suscribirse</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>Cerrar</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>Correo electrónico</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>(opcional)</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>Cancelar</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>Suscribirse</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>Cerrar</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>Error:</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>Convertir a XML</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>Convertir a JSON</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>Convertir a ICC</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>ID del perfil</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>Desplazamiento</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>Tamaño</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>Relleno</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>Tipo</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>Array de {type}</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>(Sin contenido)</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>bytes</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>Sin salida de validación</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>El perfil es válido</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>Error de validación crítico</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>Válido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>Advertencia</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>Error</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>Desconocido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>Aprobado</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>Fallido</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>Ver en contexto</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>Detalle de validación</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>Activado por</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>Campo</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>Valor actual</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>Requerido: 0</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>Esperado: {value}</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>No válido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>Cerrar</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>sangría</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>ordenar claves</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3643,791 +3643,871 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>Primarios de color</v>
+        <v>Flags del navegador</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>Características de transferencia</v>
+        <v>activado</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>no activado</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>no se puede detectar aquí</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>Rango completo</v>
+        <v>Necesario para representar HDR en este navegador: sin WebGPU, el lienzo HDR es la única vía. La inspección de perfiles funciona sin él.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>Rango reducido</v>
+        <v>Opcional: el HDR puede representarse con WebGPU, pero esto añade la vía de lienzo HDR y permite a profiletool leer el margen HDR real de la pantalla.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Las páginas web no pueden abrir páginas de flags. Pega esto en la barra de direcciones, elige Enabled y reinicia el navegador.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Copiar</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Copiado</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>INFORME</v>
+        <v>No se pudo copiar — selecciona la dirección y cópiala.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>FALLIDO</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>comprobaciones</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>Suscribirse</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>Cerrar</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>Correo electrónico</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>(opcional)</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>Cancelar</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>Suscribirse</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>Cerrar</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>Aviso de privacidad</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>Error:</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>Convertir a XML</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>Convertir a JSON</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>Convertir a ICC</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>ID del perfil</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>Desplazamiento</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>Tamaño</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>Relleno</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>Tipo</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>Array de {type}</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>(Sin contenido)</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>bytes</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>Sin salida de validación</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>El perfil es válido</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>Error de validación crítico</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>Válido</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>Advertencia</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>Error</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>Desconocido</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>Aprobado</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>Fallido</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>Ver en contexto</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>Detalle de validación</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>Activado por</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>Campo</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>Valor actual</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>Requerido: 0</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>Esperado: {value}</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>No válido</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>Cerrar</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>sangría</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>ordenar claves</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Los navegadores no pueden informar cuánto margen HDR tiene una pantalla, solo si existe una ruta HDR.</v>
+        <v>Este navegador no ha informado del margen HDR de la pantalla, solo de si existe una ruta HDR.</v>
       </c>
     </row>
     <row r="405">
@@ -3723,791 +3723,927 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>Primarios de color</v>
+        <v>Relación de píxeles</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>Características de transferencia</v>
+        <v>Monitor actual</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>sin nombre</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>principal</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>Rango completo</v>
+        <v>integrado</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>Rango reducido</v>
+        <v>Margen HDR</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>no expuesto por este navegador</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Se muestra tal como lo informa el navegador. La unidad aún no está estandarizada; una pantalla SDR informó 0.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>INFORME</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>FALLIDO</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>comprobaciones</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>Suscribirse</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>Cerrar</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>Correo electrónico</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>(opcional)</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>Cancelar</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>Suscribirse</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>Cerrar</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>Error:</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>Convertir a XML</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>Convertir a JSON</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>Convertir a ICC</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>ID del perfil</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>Desplazamiento</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>Tamaño</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Relleno</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>Tipo</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>Array de {type}</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>(Sin contenido)</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>bytes</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>Sin salida de validación</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>El perfil es válido</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>Error de validación crítico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>Válido</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>Advertencia</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>Error</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>Desconocido</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>Aprobado</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>Fallido</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>Ver en contexto</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>Detalle de validación</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>Activado por</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>Campo</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>Valor actual</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>Requerido: 0</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>Esperado: {value}</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>No válido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>Cerrar</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>Cargando editor XML…</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>sangría</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>ordenar claves</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3779,871 +3779,879 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>Se muestra tal como lo informa el navegador. La unidad aún no está estandarizada; una pantalla SDR informó 0.</v>
+        <v>Chromium lo informa en pasos: log₂ del brillo máximo de la pantalla ÷ su nivel de blanco SDR. En Windows solo se actualiza cuando Chrome vuelve a leer la pantalla —la ventana pasa a otra pantalla o Chrome vuelve a activarse—, no cuando cambia el brillo.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>{stops} pasos (≈{ratio}× el blanco SDR)</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>Identificar pantallas</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>Eventos de pantalla</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>Primarios de color</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>Características de transferencia</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>Rango completo</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>Rango reducido</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>INFORME</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>Correo electrónico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>(opcional)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>Cancelar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>Suscribirse</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>Cerrar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>Error:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3795,863 +3795,1383 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>Identificar pantallas</v>
+        <v>Ganancia a un margen de pantalla</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Ve una imagen HDR en esta pantalla. Los archivos que el navegador sabe decodificar los muestra el propio navegador; OpenEXR lo decodifica y lo representa profiletool.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Suelta aquí una imagen HDR o haz clic para elegir una</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>OpenEXR, AVIF, JPEG (incluido JPEG con gain map), PNG — y HEIC en Safari.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Elegir otra</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Perfil ICC incrustado</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>ninguno — OpenEXR indica el color mediante cromaticidades</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>Primarios de color</v>
+        <v>comprobando…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>Características de transferencia</v>
+        <v>ninguno</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Abrir en la pestaña Perfil</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Gain map</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>Rango completo</v>
+        <v>detectado, no decodificado</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>Rango reducido</v>
+        <v>Eso no es una imagen. Carga los perfiles desde el panel Perfiles.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>No es un formato de imagen que profiletool reconozca.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Los píxeles TIFF aún no se muestran aquí: los navegadores no decodifican TIFF y aún no está decidido cómo se codifica el HDR en un TIFF de 16 bits (fase 4.3). Su perfil incrustado se puede inspeccionar.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>No se puede mostrar esta imagen aquí:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>INFORME</v>
+        <v>Su perfil incrustado aún se puede inspeccionar.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>FALLIDO</v>
+        <v>Mostrado por</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>comprobaciones</v>
+        <v>el navegador</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Pantalla HDR</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Los navegadores ignoran el HDR indicado solo por un perfil ICC incrustado, así que esta imagen puede verse apagada y plana.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Este navegador no puede cambiar una imagen entre SDR y HDR, así que se muestra tal como la representa.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>Suscribirse</v>
+        <v>El navegador no pudo decodificar esta imagen.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Lienzo HDR (float16)</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>Cerrar</v>
+        <v>WebGPU (rango extendido)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Lienzo SDR (con tone mapping)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>Correo electrónico</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Píxel más brillante</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>{n}× el blanco SDR</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>(opcional)</v>
+        <v>Cromaticidades</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>no indicadas — se asume Rec. 709</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>{from} no está disponible aquí ({why}); se usa la siguiente salida.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>Cancelar</v>
+        <v>Esta salida no puede transportar valores más brillantes que el blanco, así que se muestra la representación SDR con tone mapping.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>Suscribirse</v>
+        <v>Exposición</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>{n} pasos</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>No se pudo decodificar:</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>Cerrar</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Rango dinámico</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Este navegador solo ofrece los dos extremos, no una mezcla.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>Error:</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>Convertir a XML</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>Convertir a JSON</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>Convertir a ICC</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>ID del perfil</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>Desplazamiento</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>Tamaño</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>Relleno</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>Tipo</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>Array de {type}</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>(Sin contenido)</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>bytes</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>Sin salida de validación</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>El perfil es válido</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>Error de validación crítico</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>Válido</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>Advertencia</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>Error</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>Desconocido</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>Aprobado</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>Fallido</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>Ver en contexto</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>Detalle de validación</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>Activado por</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>Campo</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>Valor actual</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>Requerido: 0</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>Esperado: {value}</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>No válido</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>Cerrar</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>Cargando editor XML…</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>sangría</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>ordenar claves</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>Aviso de privacidad</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>Introduzca una dirección de correo electrónico válida.</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>Revise el formulario e inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>Error de red. Inténtelo de nuevo.</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>Error:</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>Convertir a XML</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>Convertir a JSON</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>Convertir a ICC</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>Convirtiendo a XML…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>Convirtiendo a JSON…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>Convirtiendo a ICC…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>Cargar perfil ICC</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>Zona de soltado para archivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>ID del perfil</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>No se encontraron etiquetas.</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>Nombre de etiqueta</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>Desplazamiento</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>Tamaño</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>Relleno</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>Bytes modificados desde la carga</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>(Sin contenido)</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>Cargando descripción completa…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>No se pudo cargar la descripción completa:</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>Sin salida de validación</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>El perfil es válido</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>El perfil tiene advertencias</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>El perfil no es conforme</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>Error de validación crítico</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>Estado de validación desconocido</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>Crítico — mostrado solo para inspección</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>No se encontraron advertencias ni errores.</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>Advertencia</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3894,7 +3894,7 @@
         <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Gain map</v>
+        <v>Mapa de ganancia</v>
       </c>
     </row>
     <row r="437">
@@ -4139,1039 +4139,1175 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>decodificado por el propio profiletool, así que no depende del navegador</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>Margen de la pantalla</v>
+        <v>este navegador lo decodifica</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>este navegador no lo decodifica</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>Base</v>
+        <v>mostrar HEIC requiere Safari u otro navegador WebKit — Chrome y Firefox no decodifican HEIC en ninguna plataforma, incluido macOS</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>mostrar JPEG XL requiere Safari; los demás navegadores aún no lo admiten</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>aplazado a una versión posterior</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>esta pantalla no informa de ninguna ruta HDR, así que el HDR se muestra en SDR con tone mapping</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>este navegador no ofrece un lienzo HDR (requiere lienzo float16 o WebGPU)</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>Firefox no muestra imágenes HDR ni lee gain maps; el contenido HDR se muestra en SDR</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>la inspección solo necesita analizar el contenedor, no un códec</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>hay pantalla HDR y lienzo HDR disponibles</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>formato desconocido</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>{browser} en {os}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>{name} · pantalla HDR detectada</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>{name} · pantalla SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>WebGPU aplicó el tone mapping «{mode}», así que la salida se limita a SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Este navegador no informa del tone mapping de WebGPU aplicado, así que la salida HDR no está confirmada</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>Sin cambios</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>Identificar pantallas</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>Primarios de color</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>Características de transferencia</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>Rango completo</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>Rango reducido</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>INFORME</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>FALLIDO</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>comprobaciones</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>Suscribirse</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>Cerrar</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>Correo electrónico</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>(opcional)</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>Cancelar</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>Suscribirse</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>Cerrar</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>Error:</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>Convertir a XML</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>Convertir a JSON</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>Convertir a ICC</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>ID del perfil</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>Desplazamiento</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>Tamaño</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>Relleno</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>Tipo</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>Array de {type}</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>(Sin contenido)</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>bytes</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>Sin salida de validación</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>El perfil es válido</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>Error de validación crítico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>Válido</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>Advertencia</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>Error</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>Desconocido</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>Aprobado</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>Fallido</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>Ver en contexto</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>Detalle de validación</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>Activado por</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>Campo</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>Valor actual</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>Requerido: 0</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>Esperado: {value}</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>No válido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>Cerrar</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>Cargando editor XML…</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>sangría</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>ordenar claves</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4275,1039 +4275,1143 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Pico de la pantalla</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>Margen de la pantalla</v>
+        <v>{r}× el blanco SDR ({n} pasos)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>1× — pantalla SDR</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>Base</v>
+        <v>desconocido</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>Esta pantalla no informa de HDR, así que el navegador muestra la imagen en SDR en ambos extremos.</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Esta pantalla no informa de HDR, así que todo lo más brillante que el blanco SDR se recorta. «Ajustar a la pantalla» muestra en su lugar la representación con tone mapping.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Esta imagen pide {img}× el blanco SDR, pero esta pantalla solo llega a {disp}×, así que los valores más brillantes se recortan. «Ajustar a la pantalla» los atenúa hacia el pico de la pantalla.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Ajustar a la pantalla</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>sin límite</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>límite {n} pasos ({r}×)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Blanco SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>Sin cambios</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>Identificar pantallas</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>Primarios de color</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>Características de transferencia</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>Rango completo</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>Rango reducido</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>INFORME</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>FALLIDO</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>comprobaciones</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>Suscribirse</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>Cerrar</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>Correo electrónico</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>(opcional)</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>Cancelar</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>Error:</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>Convertir a XML</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>Convertir a JSON</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>Convertir a ICC</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>ID del perfil</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>Desplazamiento</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>Tamaño</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>Relleno</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>Tipo</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>Array de {type}</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>(Sin contenido)</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>bytes</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>Sin salida de validación</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>El perfil es válido</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>Error de validación crítico</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>Válido</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>Advertencia</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>Error</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>Desconocido</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>Aprobado</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>Fallido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>Ver en contexto</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>Detalle de validación</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>Activado por</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>Campo</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>Valor actual</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>Requerido: 0</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>Esperado: {value}</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>No válido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>Cerrar</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>sangría</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>ordenar claves</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4379,1039 +4379,1055 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Parche blanco SDR</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>Margen de la pantalla</v>
+        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Base</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>Sin cambios</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>Identificar pantallas</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>Primarios de color</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>Características de transferencia</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>Rango completo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>Rango reducido</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>INFORME</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>FALLIDO</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>comprobaciones</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>Suscribirse</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>Correo electrónico</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>(opcional)</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>Cancelar</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>Suscribirse</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>Cerrar</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>Error:</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>Convertir a XML</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>Convertir a JSON</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>ID del perfil</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>Desplazamiento</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>Tamaño</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>Relleno</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>Tipo</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>Array de {type}</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>(Sin contenido)</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>bytes</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>Sin salida de validación</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>El perfil es válido</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>Válido</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>Advertencia</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>Error</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>Desconocido</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>Aprobado</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>Fallido</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>Ver en contexto</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>Detalle de validación</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>Activado por</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>Campo</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>Valor actual</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>Requerido: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>No válido</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>Cerrar</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>ordenar claves</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4395,1039 +4395,1223 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Asignar perfil</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>Margen de la pantalla</v>
+        <v>Ninguno — según indique el archivo</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>Perfil incrustado ({n} B)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>Base</v>
+        <v>Perfiles HDR del pool</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>perfil incrustado</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Ruta del motor de color</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Ruta HDR, curva de ganancia aplicada</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>Ruta HDR, sin curva de ganancia</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>AToB0 precalculado — no es la ruta HDR</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Transferencia</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Blanco de referencia HDR</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Margen objetivo</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>{r}× el blanco de referencia ({n} pasos)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Auto (orden de la cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Curva de ganancia (HAGC)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Alternativa SDR precalculada (AToB0)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Desactivado — como un CMM anterior a la enmienda</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>Sin cambios</v>
+        <v>Aplicando el perfil…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>OpenEXR contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>Identificar pantallas</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>Primarios de color</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>Características de transferencia</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>Rango completo</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Rango reducido</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>INFORME</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>FALLIDO</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>comprobaciones</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>Suscribirse</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>Cerrar</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>Correo electrónico</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>(opcional)</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>Cancelar</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>Suscribirse</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>Cerrar</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>Aviso de privacidad</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>Error:</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>Convertir a XML</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>Convertir a JSON</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>Convertir a ICC</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>ID del perfil</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>Desplazamiento</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>Tamaño</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>Relleno</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>Tipo</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>Array de {type}</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>(Sin contenido)</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>bytes</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>Sin salida de validación</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>El perfil es válido</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>Error de validación crítico</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>Válido</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>Advertencia</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>Desconocido</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>Aprobado</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>Fallido</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>Ver en contexto</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>Detalle de validación</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>Activado por</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>Campo</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>Valor actual</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>Requerido: 0</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>Esperado: {value}</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>No válido</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>Cerrar</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>Cargando editor XML…</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>sangría</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>ordenar claves</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4579,1039 +4579,1103 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Perfiles HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>Margen de la pantalla</v>
+        <v>Transferencia lineal</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>Transferencia no lineal (PQ, HLG)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>Base</v>
+        <v>Perfiles HDR — transferencia lineal</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>Perfiles HDR — transferencia PQ / HLG</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>OpenEXR contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>Sin cambios</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>Identificar pantallas</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>Primarios de color</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>Características de transferencia</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>Rango completo</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>Rango reducido</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>INFORME</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>FALLIDO</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>comprobaciones</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>Suscribirse</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>Cerrar</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>Correo electrónico</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>(opcional)</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>Cancelar</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>Suscribirse</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>Cerrar</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>Aviso de privacidad</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>Error:</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Convertir a XML</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>Convertir a JSON</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>Convertir a ICC</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>ID del perfil</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>Desplazamiento</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>Tamaño</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>Relleno</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>Tipo</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>Array de {type}</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>(Sin contenido)</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>Sin salida de validación</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>El perfil es válido</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>El perfil no es conforme</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>Error de validación crítico</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>Válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>Advertencia</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>Error</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>Desconocido</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>Aprobado</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>Fallido</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>Ver en contexto</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>Detalle de validación</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>Activado por</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>Campo</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>Valor actual</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>Requerido: 0</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>Esperado: {value}</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>No válido</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>Cerrar</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>sangría</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>ordenar claves</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Ve una imagen HDR en esta pantalla. Los archivos que el navegador sabe decodificar los muestra el propio navegador; OpenEXR lo decodifica y lo representa profiletool.</v>
+        <v>Ve una imagen HDR en esta pantalla. Los archivos que el navegador sabe decodificar los muestra el propio navegador; OpenEXR y Radiance HDR los decodifica y representa profiletool.</v>
       </c>
     </row>
     <row r="427">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, AVIF, JPEG (incluido JPEG con gain map), PNG — y HEIC en Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluido JPEG con gain map), PNG — y HEIC en Safari.</v>
       </c>
     </row>
     <row r="429">
@@ -3867,1815 +3867,1823 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>comprobando…</v>
+        <v>ninguno — Radiance HDR indica el color mediante su cabecera PRIMARIES</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>ninguno</v>
+        <v>comprobando…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>Abrir en la pestaña Perfil</v>
+        <v>ninguno</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>Mapa de ganancia</v>
+        <v>Abrir en la pestaña Perfil</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>detectado, no decodificado</v>
+        <v>Mapa de ganancia</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>Eso no es una imagen. Carga los perfiles desde el panel Perfiles.</v>
+        <v>detectado, no decodificado</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>No es un formato de imagen que profiletool reconozca.</v>
+        <v>Eso no es una imagen. Carga los perfiles desde el panel Perfiles.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>Los píxeles TIFF aún no se muestran aquí: los navegadores no decodifican TIFF y aún no está decidido cómo se codifica el HDR en un TIFF de 16 bits (fase 4.3). Su perfil incrustado se puede inspeccionar.</v>
+        <v>No es un formato de imagen que profiletool reconozca.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>No se puede mostrar esta imagen aquí:</v>
+        <v>Los píxeles TIFF aún no se muestran aquí: los navegadores no decodifican TIFF y aún no está decidido cómo se codifica el HDR en un TIFF de 16 bits (fase 4.3). Su perfil incrustado se puede inspeccionar.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>Su perfil incrustado aún se puede inspeccionar.</v>
+        <v>No se puede mostrar esta imagen aquí:</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>Mostrado por</v>
+        <v>Su perfil incrustado aún se puede inspeccionar.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>el navegador</v>
+        <v>Mostrado por</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>el navegador</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>Pantalla HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>Los navegadores ignoran el HDR indicado solo por un perfil ICC incrustado, así que esta imagen puede verse apagada y plana.</v>
+        <v>Pantalla HDR</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>Este navegador no puede cambiar una imagen entre SDR y HDR, así que se muestra tal como la representa.</v>
+        <v>Los navegadores ignoran el HDR indicado solo por un perfil ICC incrustado, así que esta imagen puede verse apagada y plana.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>El navegador no pudo decodificar esta imagen.</v>
+        <v>Este navegador no puede cambiar una imagen entre SDR y HDR, así que se muestra tal como la representa.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>Salida</v>
+        <v>El navegador no pudo decodificar esta imagen.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>Lienzo HDR (float16)</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU (rango extendido)</v>
+        <v>Lienzo HDR (float16)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>Lienzo SDR (con tone mapping)</v>
+        <v>WebGPU (rango extendido)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>Tamaño</v>
+        <v>Lienzo SDR (con tone mapping)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>Píxel más brillante</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>{n}× el blanco SDR</v>
+        <v>Píxel más brillante</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>Cromaticidades</v>
+        <v>{n}× el blanco SDR</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>no indicadas — se asume Rec. 709</v>
+        <v>Cromaticidades</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from} no está disponible aquí ({why}); se usa la siguiente salida.</v>
+        <v>no indicadas — se asume Rec. 709</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>Esta salida no puede transportar valores más brillantes que el blanco, así que se muestra la representación SDR con tone mapping.</v>
+        <v>{from} no está disponible aquí ({why}); se usa la siguiente salida.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>Exposición</v>
+        <v>Esta salida no puede transportar valores más brillantes que el blanco, así que se muestra la representación SDR con tone mapping.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} pasos</v>
+        <v>Exposición</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>No se pudo decodificar:</v>
+        <v>{n} pasos</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>Decodificando…</v>
+        <v>No se pudo decodificar:</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>Rango dinámico</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>Este navegador solo ofrece los dos extremos, no una mezcla.</v>
+        <v>Rango dinámico</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>decodificado por el propio profiletool, así que no depende del navegador</v>
+        <v>Este navegador solo ofrece los dos extremos, no una mezcla.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>este navegador lo decodifica</v>
+        <v>decodificado por el propio profiletool, así que no depende del navegador</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>este navegador no lo decodifica</v>
+        <v>este navegador lo decodifica</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>mostrar HEIC requiere Safari u otro navegador WebKit — Chrome y Firefox no decodifican HEIC en ninguna plataforma, incluido macOS</v>
+        <v>este navegador no lo decodifica</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>mostrar JPEG XL requiere Safari; los demás navegadores aún no lo admiten</v>
+        <v>mostrar HEIC requiere Safari u otro navegador WebKit — Chrome y Firefox no decodifican HEIC en ninguna plataforma, incluido macOS</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>aplazado a una versión posterior</v>
+        <v>mostrar JPEG XL requiere Safari; los demás navegadores aún no lo admiten</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>esta pantalla no informa de ninguna ruta HDR, así que el HDR se muestra en SDR con tone mapping</v>
+        <v>aplazado a una versión posterior</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>este navegador no ofrece un lienzo HDR (requiere lienzo float16 o WebGPU)</v>
+        <v>esta pantalla no informa de ninguna ruta HDR, así que el HDR se muestra en SDR con tone mapping</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox no muestra imágenes HDR ni lee gain maps; el contenido HDR se muestra en SDR</v>
+        <v>este navegador no ofrece un lienzo HDR (requiere lienzo float16 o WebGPU)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>la inspección solo necesita analizar el contenedor, no un códec</v>
+        <v>Firefox no muestra imágenes HDR ni lee gain maps; el contenido HDR se muestra en SDR</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>hay pantalla HDR y lienzo HDR disponibles</v>
+        <v>la inspección solo necesita analizar el contenedor, no un códec</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>formato desconocido</v>
+        <v>hay pantalla HDR y lienzo HDR disponibles</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{browser} en {os}</v>
+        <v>formato desconocido</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · pantalla HDR detectada</v>
+        <v>{browser} en {os}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · pantalla SDR</v>
+        <v>{name} · pantalla HDR detectada</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU aplicó el tone mapping «{mode}», así que la salida se limita a SDR</v>
+        <v>{name} · pantalla SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>Este navegador no informa del tone mapping de WebGPU aplicado, así que la salida HDR no está confirmada</v>
+        <v>WebGPU aplicó el tone mapping «{mode}», así que la salida se limita a SDR</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>Pico de la pantalla</v>
+        <v>Este navegador no informa del tone mapping de WebGPU aplicado, así que la salida HDR no está confirmada</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>{r}× el blanco SDR ({n} pasos)</v>
+        <v>Pico de la pantalla</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× — pantalla SDR</v>
+        <v>{r}× el blanco SDR ({n} pasos)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>desconocido</v>
+        <v>1× — pantalla SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>Esta pantalla no informa de HDR, así que el navegador muestra la imagen en SDR en ambos extremos.</v>
+        <v>desconocido</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>Esta pantalla no informa de HDR, así que todo lo más brillante que el blanco SDR se recorta. «Ajustar a la pantalla» muestra en su lugar la representación con tone mapping.</v>
+        <v>Esta pantalla no informa de HDR, así que el navegador muestra la imagen en SDR en ambos extremos.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Esta imagen pide {img}× el blanco SDR, pero esta pantalla solo llega a {disp}×, así que los valores más brillantes se recortan. «Ajustar a la pantalla» los atenúa hacia el pico de la pantalla.</v>
+        <v>Esta pantalla no informa de HDR, así que todo lo más brillante que el blanco SDR se recorta. «Ajustar a la pantalla» muestra en su lugar la representación con tone mapping.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>Ajustar a la pantalla</v>
+        <v>Esta imagen pide {img}× el blanco SDR, pero esta pantalla solo llega a {disp}×, así que los valores más brillantes se recortan. «Ajustar a la pantalla» los atenúa hacia el pico de la pantalla.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
+        <v>Ajustar a la pantalla</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>sin límite</v>
+        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>límite {n} pasos ({r}×)</v>
+        <v>sin límite</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>Blanco SDR</v>
+        <v>límite {n} pasos ({r}×)</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
+        <v>Blanco SDR</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>Parche blanco SDR</v>
+        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
+        <v>Parche blanco SDR</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>Asignar perfil</v>
+        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>Ninguno — según indique el archivo</v>
+        <v>Asignar perfil</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>Perfil incrustado ({n} B)</v>
+        <v>Ninguno — según indique el archivo</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>Perfiles HDR del pool</v>
+        <v>Perfil incrustado ({n} B)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>Perfil</v>
+        <v>Perfiles HDR del pool</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>perfil incrustado</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>Ruta del motor de color</v>
+        <v>perfil incrustado</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>Ruta HDR, curva de ganancia aplicada</v>
+        <v>Ruta del motor de color</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>Ruta HDR, sin curva de ganancia</v>
+        <v>Ruta HDR, curva de ganancia aplicada</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>AToB0 precalculado — no es la ruta HDR</v>
+        <v>Ruta HDR, sin curva de ganancia</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>Transferencia</v>
+        <v>AToB0 precalculado — no es la ruta HDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>Blanco de referencia HDR</v>
+        <v>Transferencia</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>Margen objetivo</v>
+        <v>Blanco de referencia HDR</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>{r}× el blanco de referencia ({n} pasos)</v>
+        <v>Margen objetivo</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× el blanco de referencia ({n} pasos)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>Auto (orden de la cláusula 8.10.3)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>Curva de ganancia (HAGC)</v>
+        <v>Auto (orden de la cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>Alternativa SDR precalculada (AToB0)</v>
+        <v>Curva de ganancia (HAGC)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>Desactivado — como un CMM anterior a la enmienda</v>
+        <v>Alternativa SDR precalculada (AToB0)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>Aplicando el perfil…</v>
+        <v>Desactivado — como un CMM anterior a la enmienda</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
+        <v>Aplicando el perfil…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
+        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
+        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>Perfiles HDR</v>
+        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>Transferencia lineal</v>
+        <v>Perfiles HDR</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>Transferencia no lineal (PQ, HLG)</v>
+        <v>Transferencia lineal</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>Perfiles HDR — transferencia lineal</v>
+        <v>Transferencia no lineal (PQ, HLG)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Perfiles HDR — transferencia PQ / HLG</v>
+        <v>Perfiles HDR — transferencia lineal</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
+        <v>Perfiles HDR — transferencia PQ / HLG</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
+        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
+        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>Margen de la pantalla</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>Base</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>Sin cambios</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>Identificar pantallas</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>Eventos de pantalla</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>Primarios de color</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>Características de transferencia</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>Rango completo</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>Rango reducido</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>INFORME</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>Correo electrónico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>(opcional)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>Cancelar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>Suscribirse</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>Cerrar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>Error:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4347,1343 +4347,1431 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
+        <v>Detalles de la imagen</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>sin límite</v>
+        <v>no disponible — el navegador representa esta imagen y no puede limitarla a un pico dado</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>límite {n} pasos ({r}×)</v>
+        <v>no disponible — esta salida no muestra nada por encima del blanco SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>Blanco SDR</v>
+        <v>no disponible — no se conoce el pico de esta pantalla</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
+        <v>Acercar</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>Parche blanco SDR</v>
+        <v>Alejar</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
+        <v>Ajustar imagen</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>Asignar perfil</v>
+        <v>Píxeles reales (1:1)</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>Ninguno — según indique el archivo</v>
+        <v>Arrastra para desplazar · Ctrl+rueda para hacer zoom · doble clic para restablecer</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>Perfil incrustado ({n} B)</v>
+        <v>Arrastra para cambiar el tamaño del área de imagen; doble clic para volver al tamaño predeterminado</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>Perfiles HDR del pool</v>
+        <v>Vista de la imagen</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>Perfil</v>
+        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>perfil incrustado</v>
+        <v>sin límite</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>Ruta del motor de color</v>
+        <v>límite {n} pasos ({r}×)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>Ruta HDR, curva de ganancia aplicada</v>
+        <v>Blanco SDR</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>Ruta HDR, sin curva de ganancia</v>
+        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>AToB0 precalculado — no es la ruta HDR</v>
+        <v>Parche blanco SDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>Transferencia</v>
+        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>Blanco de referencia HDR</v>
+        <v>Asignar perfil</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>Margen objetivo</v>
+        <v>Ninguno — según indique el archivo</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>{r}× el blanco de referencia ({n} pasos)</v>
+        <v>Perfil incrustado ({n} B)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>Tone mapping</v>
+        <v>Perfiles HDR del pool</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>Auto (orden de la cláusula 8.10.3)</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>Curva de ganancia (HAGC)</v>
+        <v>perfil incrustado</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>Alternativa SDR precalculada (AToB0)</v>
+        <v>Ruta del motor de color</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>Desactivado — como un CMM anterior a la enmienda</v>
+        <v>Ruta HDR, curva de ganancia aplicada</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>Aplicando el perfil…</v>
+        <v>Ruta HDR, sin curva de ganancia</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
+        <v>AToB0 precalculado — no es la ruta HDR</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
+        <v>Transferencia</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
+        <v>Blanco de referencia HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Perfiles HDR</v>
+        <v>Margen objetivo</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>Transferencia lineal</v>
+        <v>{r}× el blanco de referencia ({n} pasos)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>Transferencia no lineal (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>Perfiles HDR — transferencia lineal</v>
+        <v>Auto (orden de la cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>Perfiles HDR — transferencia PQ / HLG</v>
+        <v>Curva de ganancia (HAGC)</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
+        <v>Alternativa SDR precalculada (AToB0)</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
+        <v>Desactivado — como un CMM anterior a la enmienda</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
+        <v>Aplicando el perfil…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>Margen de la pantalla</v>
+        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>Base</v>
+        <v>Perfiles HDR</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>Transferencia lineal</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Transferencia no lineal (PQ, HLG)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Perfiles HDR — transferencia lineal</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Perfiles HDR — transferencia PQ / HLG</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>Sin cambios</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>Identificar pantallas</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Primarios de color</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>Características de transferencia</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>Rango completo</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>Rango reducido</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>INFORME</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>FALLIDO</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>comprobaciones</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>Suscribirse</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>Cerrar</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>Correo electrónico</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>(opcional)</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Cancelar</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>Suscribirse</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>Cerrar</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>Error:</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>Convertir a XML</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>Convertir a JSON</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>Convertir a ICC</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>ID del perfil</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>Desplazamiento</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>Tamaño</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>Relleno</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>Tipo</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>Array de {type}</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>(Sin contenido)</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>bytes</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>Sin salida de validación</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>El perfil es válido</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>Error de validación crítico</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>Válido</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>Advertencia</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>Error</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>Desconocido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>Aprobado</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>Fallido</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>Ver en contexto</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>Detalle de validación</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>Activado por</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>Campo</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>Valor actual</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>Requerido: 0</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>Esperado: {value}</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>No válido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>Cerrar</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>sangría</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>ordenar claves</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4771,1007 +4771,1191 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>Vista previa a través del motor de color</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Mapeado para {h} pasos</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>blanco de referencia</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>pico de la pantalla</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Vista previa no disponible: {why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>el motor de color no tomó la ruta HDR para este perfil</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Ganancia en todos los márgenes</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Margen de la pantalla (pasos)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Ganancia (pasos)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Curva de la etiqueta</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>Sin cambios</v>
+        <v>Control</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Entrada = pico de la pantalla</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Curvas tonales de gris por margen</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>Identificar pantallas</v>
+        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>{h} pasos</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>{h} pasos (base)</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>A {h} pasos (control)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>Primarios de color</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>Características de transferencia</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>Rango completo</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>Rango reducido</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>INFORME</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>FALLIDO</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>comprobaciones</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>Suscribirse</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>Cerrar</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>Correo electrónico</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>(opcional)</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>Cancelar</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>Suscribirse</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>Cerrar</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>Aviso de privacidad</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>Error:</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>Convertir a XML</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>Convertir a JSON</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>Convertir a ICC</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>ID del perfil</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Desplazamiento</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>Tamaño</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>Relleno</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>Tipo</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>Array de {type}</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>(Sin contenido)</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>bytes</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>Sin salida de validación</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>El perfil es válido</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>Error de validación crítico</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>Válido</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>Advertencia</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>Desconocido</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>Aprobado</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>Fallido</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>Ver en contexto</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>Detalle de validación</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>Activado por</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>Campo</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>Valor actual</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>Requerido: 0</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>Esperado: {value}</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>No válido</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>Cerrar</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>Cargando editor XML…</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>sangría</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>ordenar claves</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>Desconocido</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>Aprobado</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>Fallido</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>Ver en contexto</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>Detalle de validación</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>Activado por</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>Valor actual</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>Requerido: 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>No válido</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>Cerrar</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>Cargando editor XML…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>Cargando editor JSON…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4587,1375 +4587,1431 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>Margen objetivo</v>
+        <v>Valores lineales</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>{r}× el blanco de referencia ({n} pasos)</v>
+        <v>Archivo 1,0 = blanco de referencia HDR</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>Tone mapping</v>
+        <v>Archivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>Auto (orden de la cláusula 8.10.3)</v>
+        <v>Los archivos OpenEXR y Radiance HDR sitúan por convención el blanco SDR en 1,0, mientras que una transferencia ICC lineal lee 1,0 como 1 cd/m². De forma predeterminada, el archivo se escala para que su 1,0 caiga en el blanco de referencia HDR del perfil.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>Curva de ganancia (HAGC)</v>
+        <v>Escala de entrada</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Alternativa SDR precalculada (AToB0)</v>
+        <v>×{w} — archivo 1,0 = blanco de referencia</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>Desactivado — como un CMM anterior a la enmienda</v>
+        <v>ninguna — archivo 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>Aplicando el perfil…</v>
+        <v>Margen objetivo</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
+        <v>{r}× el blanco de referencia ({n} pasos)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
+        <v>Auto (orden de la cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>Perfiles HDR</v>
+        <v>Curva de ganancia (HAGC)</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>Transferencia lineal</v>
+        <v>Alternativa SDR precalculada (AToB0)</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>Transferencia no lineal (PQ, HLG)</v>
+        <v>Desactivado — como un CMM anterior a la enmienda</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>Perfiles HDR — transferencia lineal</v>
+        <v>Aplicando el perfil…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>Perfiles HDR — transferencia PQ / HLG</v>
+        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
+        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
+        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
+        <v>Perfiles HDR</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Transferencia lineal</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>Margen de la pantalla</v>
+        <v>Transferencia no lineal (PQ, HLG)</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>Perfiles HDR — transferencia lineal</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>Base</v>
+        <v>Perfiles HDR — transferencia PQ / HLG</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>Vista previa a través del motor de color</v>
+        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
+        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>Mapeado para {h} pasos</v>
+        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>blanco de referencia</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>pico de la pantalla</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>Vista previa no disponible: {why}</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>el motor de color no tomó la ruta HDR para este perfil</v>
+        <v>Vista previa a través del motor de color</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>Ganancia en todos los márgenes</v>
+        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
+        <v>Mapeado para {h} pasos</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
+        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>Margen de la pantalla (pasos)</v>
+        <v>blanco de referencia</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>Ganancia (pasos)</v>
+        <v>pico de la pantalla</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>Curva de la etiqueta</v>
+        <v>Vista previa no disponible: {why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Base</v>
+        <v>el motor de color no tomó la ruta HDR para este perfil</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>Control</v>
+        <v>Ganancia en todos los márgenes</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>Entrada = pico de la pantalla</v>
+        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>Curvas tonales de gris por margen</v>
+        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
+        <v>Margen de la pantalla (pasos)</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
+        <v>Ganancia (pasos)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} pasos</v>
+        <v>Curva de la etiqueta</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} pasos (base)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>A {h} pasos (control)</v>
+        <v>Control</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>Entrada = pico de la pantalla</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Curvas tonales de gris por margen</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>{h} pasos</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>{h} pasos (base)</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>A {h} pasos (control)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>Sin cambios</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>Identificar pantallas</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>Eventos de pantalla</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>Primarios de color</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>Características de transferencia</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>Rango completo</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>Rango reducido</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>INFORME</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>FALLIDO</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>comprobaciones</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>Suscribirse</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>Cerrar</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>Correo electrónico</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>(opcional)</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>Cancelar</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>Suscribirse</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>Cerrar</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>Aviso de privacidad</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>Error:</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>Convertir a XML</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>Convertir a JSON</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>Convertir a ICC</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>ID del perfil</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>Desplazamiento</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>Tamaño</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>Relleno</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>Tipo</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>Array de {type}</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>(Sin contenido)</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>bytes</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>Sin salida de validación</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>El perfil es válido</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>Error de validación crítico</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Válido</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>Advertencia</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>Error</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>Desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>Aprobado</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>Fallido</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>Ver en contexto</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Detalle de validación</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>Activado por</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>Campo</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>Valor actual</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>Requerido: 0</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>Esperado: {value}</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>No válido</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>Cerrar</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>sangría</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>ordenar claves</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● ediciones XML sin guardar</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -4662,7 +4662,7 @@
         <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Tone mapping</v>
+        <v>Mapeo de tonos</v>
       </c>
     </row>
     <row r="533">

--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4123,1895 +4123,1935 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>Decodificando…</v>
+        <v>Este archivo ocupa {size} MB; la pestaña HDR abre imágenes de hasta {max} MB.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>Rango dinámico</v>
+        <v>No se pudo aplicar el perfil:</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>Este navegador solo ofrece los dos extremos, no una mezcla.</v>
+        <v>No se pudo dibujar la imagen:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>decodificado por el propio profiletool, así que no depende del navegador</v>
+        <v>(estos primarios no definen un espacio de color — se ignoran y se usa Rec. 709)</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>este navegador lo decodifica</v>
+        <v>el perfil de un JPEG XL está comprimido dentro del codestream, que profiletool aún no descomprime</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>este navegador no lo decodifica</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>mostrar HEIC requiere Safari u otro navegador WebKit — Chrome y Firefox no decodifican HEIC en ninguna plataforma, incluido macOS</v>
+        <v>Rango dinámico</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>mostrar JPEG XL requiere Safari; los demás navegadores aún no lo admiten</v>
+        <v>Este navegador solo ofrece los dos extremos, no una mezcla.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>aplazado a una versión posterior</v>
+        <v>decodificado por el propio profiletool, así que no depende del navegador</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>esta pantalla no informa de ninguna ruta HDR, así que el HDR se muestra en SDR con tone mapping</v>
+        <v>este navegador lo decodifica</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>este navegador no ofrece un lienzo HDR (requiere lienzo float16 o WebGPU)</v>
+        <v>este navegador no lo decodifica</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox no muestra imágenes HDR ni lee gain maps; el contenido HDR se muestra en SDR</v>
+        <v>mostrar HEIC requiere Safari u otro navegador WebKit — Chrome y Firefox no decodifican HEIC en ninguna plataforma, incluido macOS</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>la inspección solo necesita analizar el contenedor, no un códec</v>
+        <v>mostrar JPEG XL requiere Safari; los demás navegadores aún no lo admiten</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>hay pantalla HDR y lienzo HDR disponibles</v>
+        <v>aplazado a una versión posterior</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>formato desconocido</v>
+        <v>esta pantalla no informa de ninguna ruta HDR, así que el HDR se muestra en SDR con tone mapping</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{browser} en {os}</v>
+        <v>este navegador no ofrece un lienzo HDR (requiere lienzo float16 o WebGPU)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · pantalla HDR detectada</v>
+        <v>Firefox no muestra imágenes HDR ni lee gain maps; el contenido HDR se muestra en SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · pantalla SDR</v>
+        <v>la inspección solo necesita analizar el contenedor, no un códec</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU aplicó el tone mapping «{mode}», así que la salida se limita a SDR</v>
+        <v>hay pantalla HDR y lienzo HDR disponibles</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>Este navegador no informa del tone mapping de WebGPU aplicado, así que la salida HDR no está confirmada</v>
+        <v>formato desconocido</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>Pico de la pantalla</v>
+        <v>{browser} en {os}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>{r}× el blanco SDR ({n} pasos)</v>
+        <v>{name} · pantalla HDR detectada</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× — pantalla SDR</v>
+        <v>{name} · pantalla SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>desconocido</v>
+        <v>WebGPU aplicó el tone mapping «{mode}», así que la salida se limita a SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>Esta pantalla no informa de HDR, así que el navegador muestra la imagen en SDR en ambos extremos.</v>
+        <v>Este navegador no informa del tone mapping de WebGPU aplicado, así que la salida HDR no está confirmada</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>Esta pantalla no informa de HDR, así que todo lo más brillante que el blanco SDR se recorta. «Ajustar a la pantalla» muestra en su lugar la representación con tone mapping.</v>
+        <v>Pico de la pantalla</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>Esta imagen pide {img}× el blanco SDR, pero esta pantalla solo llega a {disp}×, así que los valores más brillantes se recortan. «Ajustar a la pantalla» los atenúa hacia el pico de la pantalla.</v>
+        <v>{r}× el blanco SDR ({n} pasos)</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>Ajustar a la pantalla</v>
+        <v>1× — pantalla SDR</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>Detalles de la imagen</v>
+        <v>desconocido</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>no disponible — el navegador representa esta imagen y no puede limitarla a un pico dado</v>
+        <v>Esta pantalla no informa de HDR, así que el navegador muestra la imagen en SDR en ambos extremos.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>no disponible — esta salida no muestra nada por encima del blanco SDR</v>
+        <v>Esta pantalla no informa de HDR, así que todo lo más brillante que el blanco SDR se recorta. «Ajustar a la pantalla» muestra en su lugar la representación con tone mapping.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>no disponible — no se conoce el pico de esta pantalla</v>
+        <v>Esta imagen pide {img}× el blanco SDR, pero esta pantalla solo llega a {disp}×, así que los valores más brillantes se recortan. «Ajustar a la pantalla» los atenúa hacia el pico de la pantalla.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>Acercar</v>
+        <v>Ajustar a la pantalla</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>Alejar</v>
+        <v>Detalles de la imagen</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>Ajustar imagen</v>
+        <v>no disponible — el navegador representa esta imagen y no puede limitarla a un pico dado</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>Píxeles reales (1:1)</v>
+        <v>no disponible — esta salida no muestra nada por encima del blanco SDR</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>Arrastra para desplazar · Ctrl+rueda para hacer zoom · doble clic para restablecer</v>
+        <v>no disponible — no se conoce el pico de esta pantalla</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>Arrastra para cambiar el tamaño del área de imagen; doble clic para volver al tamaño predeterminado</v>
+        <v>Acercar</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>Vista de la imagen</v>
+        <v>Alejar</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
+        <v>Ajustar imagen</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>sin límite</v>
+        <v>Píxeles reales (1:1)</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>límite {n} pasos ({r}×)</v>
+        <v>Arrastra para desplazar · Ctrl+rueda para hacer zoom · doble clic para restablecer</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>Blanco SDR</v>
+        <v>Arrastra para cambiar el tamaño del área de imagen; doble clic para volver al tamaño predeterminado</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
+        <v>Vista de la imagen</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>Parche blanco SDR</v>
+        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
+        <v>sin límite</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>Asignar perfil</v>
+        <v>límite {n} pasos ({r}×)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>Ninguno — según indique el archivo</v>
+        <v>Blanco SDR</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>Perfil incrustado ({n} B)</v>
+        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>Perfiles HDR del pool</v>
+        <v>Parche blanco SDR</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>Perfil</v>
+        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>perfil incrustado</v>
+        <v>Asignar perfil</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>Ruta del motor de color</v>
+        <v>Ninguno — según indique el archivo</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>Ruta HDR, curva de ganancia aplicada</v>
+        <v>Perfil incrustado ({n} B)</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>Ruta HDR, sin curva de ganancia</v>
+        <v>Perfiles HDR del pool</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>AToB0 precalculado — no es la ruta HDR</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>Transferencia</v>
+        <v>perfil incrustado</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>Blanco de referencia HDR</v>
+        <v>Ruta del motor de color</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>Valores lineales</v>
+        <v>Ruta HDR, curva de ganancia aplicada</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>Archivo 1,0 = blanco de referencia HDR</v>
+        <v>Ruta HDR, sin curva de ganancia</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>Archivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>AToB0 precalculado — no es la ruta HDR</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Los archivos OpenEXR y Radiance HDR sitúan por convención el blanco SDR en 1,0, mientras que una transferencia ICC lineal lee 1,0 como 1 cd/m². De forma predeterminada, el archivo se escala para que su 1,0 caiga en el blanco de referencia HDR del perfil.</v>
+        <v>Transferencia</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>Escala de entrada</v>
+        <v>Blanco de referencia HDR</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} — archivo 1,0 = blanco de referencia</v>
+        <v>Valores lineales</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>ninguna — archivo 1,0 = 1 cd/m²</v>
+        <v>Archivo 1,0 = blanco de referencia HDR</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>Margen objetivo</v>
+        <v>Archivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>{r}× el blanco de referencia ({n} pasos)</v>
+        <v>Los archivos OpenEXR y Radiance HDR sitúan por convención el blanco SDR en 1,0, mientras que una transferencia ICC lineal lee 1,0 como 1 cd/m². De forma predeterminada, el archivo se escala para que su 1,0 caiga en el blanco de referencia HDR del perfil.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>Mapeo de tonos</v>
+        <v>Escala de entrada</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>Auto (orden de la cláusula 8.10.3)</v>
+        <v>×{w} — archivo 1,0 = blanco de referencia</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>Curva de ganancia (HAGC)</v>
+        <v>ninguna — archivo 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Alternativa SDR precalculada (AToB0)</v>
+        <v>Margen objetivo</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>Desactivado — como un CMM anterior a la enmienda</v>
+        <v>{r}× el blanco de referencia ({n} pasos)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>Aplicando el perfil…</v>
+        <v>Mapeo de tonos</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
+        <v>Auto (orden de la cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
+        <v>Curva de ganancia (HAGC)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
+        <v>Alternativa SDR precalculada (AToB0)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>Perfiles HDR</v>
+        <v>Desactivado — como un CMM anterior a la enmienda</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>Transferencia lineal</v>
+        <v>Aplicando el perfil…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>Transferencia no lineal (PQ, HLG)</v>
+        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>Perfiles HDR — transferencia lineal</v>
+        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>Perfiles HDR — transferencia PQ / HLG</v>
+        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
+        <v>Perfiles HDR</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
+        <v>Transferencia lineal</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
+        <v>Transferencia no lineal (PQ, HLG)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Perfiles HDR — transferencia lineal</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Margen de la pantalla</v>
+        <v>Perfiles HDR — transferencia PQ / HLG</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>Base</v>
+        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Vista previa a través del motor de color</v>
+        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Mapeado para {h} pasos</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>blanco de referencia</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>pico de la pantalla</v>
+        <v>Vista previa a través del motor de color</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>Vista previa no disponible: {why}</v>
+        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>el motor de color no tomó la ruta HDR para este perfil</v>
+        <v>Mapeado para {h} pasos</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>Ganancia en todos los márgenes</v>
+        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
+        <v>blanco de referencia</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
+        <v>pico de la pantalla</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>Margen de la pantalla (pasos)</v>
+        <v>Vista previa no disponible: {why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>Ganancia (pasos)</v>
+        <v>el motor de color no tomó la ruta HDR para este perfil</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>Curva de la etiqueta</v>
+        <v>Ganancia en todos los márgenes</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>Base</v>
+        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>Control</v>
+        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>Entrada = pico de la pantalla</v>
+        <v>Margen de la pantalla (pasos)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Curvas tonales de gris por margen</v>
+        <v>Ganancia (pasos)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
+        <v>Curva de la etiqueta</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} pasos</v>
+        <v>Control</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} pasos (base)</v>
+        <v>Entrada = pico de la pantalla</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>A {h} pasos (control)</v>
+        <v>Curvas tonales de gris por margen</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>{h} pasos</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>{h} pasos (base)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>A {h} pasos (control)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>Sin cambios</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Identificar pantallas</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>Eventos de pantalla</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>Primarios de color</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>Características de transferencia</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>Rango completo</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>Rango reducido</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>INFORME</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>FALLIDO</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>comprobaciones</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>Suscribirse</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>Cerrar</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Correo electrónico</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>(opcional)</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>Cancelar</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>Suscribirse</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>Cerrar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>Error:</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>Convertir a XML</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>Convertir a JSON</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Convertir a ICC</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>ID del perfil</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>Desplazamiento</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>Tamaño</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>Relleno</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>Tipo</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>Array de {type}</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>(Sin contenido)</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>bytes</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>Sin salida de validación</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>El perfil es válido</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>El perfil no es conforme</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>Error de validación crítico</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>Válido</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>Advertencia</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>Error</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>Desconocido</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>Aprobado</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>Fallido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>Ver en contexto</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>Detalle de validación</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>Activado por</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>Campo</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>Valor actual</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>Requerido: 0</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>Esperado: {value}</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>No válido</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>Cerrar</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>sangría</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>ordenar claves</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● ediciones JSON sin guardar</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>sangría</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluido JPEG con gain map), PNG — y HEIC en Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluido JPEG con gain map), PNG — y HEIC y JPEG XL en Safari.</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se descarga.</v>
+        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se abre; no se descarga nada hasta que pulses Guardar perfil ICC.</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,4861 +1197,4869 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Ordenar por nombre</v>
+        <v>Toca para seleccionar y luego toca una pestaña para enviar.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nombre</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Nuevo perfil desde .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se abre; no se descarga nada hasta que pulses Guardar perfil ICC.</v>
+        <v>Nuevo perfil desde .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Elegir archivo .cube</v>
+        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se abre; no se descarga nada hasta que pulses Guardar perfil ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Elegir archivo .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>o suéltalo aquí, o pega debajo</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Creando…</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Perfil</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Enlazar</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Espectral</v>
+        <v>Enlazar</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Arrastra perfiles del conjunto a esta pestaña</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Quitar</v>
+        <v>Arrastra perfiles del conjunto a esta pestaña</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Ningún perfil seleccionado</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
+        <v>Ningún perfil seleccionado</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Aún no hay nada que comparar</v>
+        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
+        <v>Aún no hay nada que comparar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Comparación de gama</v>
+        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
+        <v>Comparación de gama</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Propósito de representación</v>
+        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Envoltura</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Malla</v>
+        <v>Envoltura</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Números de eje</v>
+        <v>Malla</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacidad</v>
+        <v>Números de eje</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Color</v>
+        <v>Opacidad</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Sólido</v>
+        <v>Color</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Por tono</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotación</v>
+        <v>Por tono</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Plataforma giratoria</v>
+        <v>Rotación</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Órbita</v>
+        <v>Plataforma giratoria</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocidad de arrastre</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Alabeo</v>
+        <v>Velocidad de arrastre</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Velocidad de alabeo</v>
+        <v>Alabeo</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Construyendo la gama…</v>
+        <v>Velocidad de alabeo</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>sin gama</v>
+        <v>Construyendo la gama…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sin gama</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Envoltura de gama 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Corte de gama 2D</v>
+        <v>Envoltura de gama 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plano</v>
+        <v>Corte de gama 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Enlace</v>
+        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
+        <v>Enlace</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
+        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Creador de pantalla V4</v>
+        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
+        <v>Creador de pantalla V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Pantalla RGB V5</v>
+        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>suelta un perfil de pantalla</v>
+        <v>Pantalla RGB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>suelta un perfil de pantalla</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>suelta un perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
+        <v>suelta un perfil de observador</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Crear perfil de pantalla V4</v>
+        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nombre del perfil</v>
+        <v>Crear perfil de pantalla V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Crear</v>
+        <v>Nombre del perfil</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Creando…</v>
+        <v>Crear</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Flujo de enlace</v>
+        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
+        <v>Flujo de enlace</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Hecho</v>
+        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
+        <v>Hecho</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Comprobando imagen…</v>
+        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
+        <v>Comprobando imagen…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
+        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformar imagen</v>
+        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Transformando…</v>
+        <v>Transformar imagen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Suelta perfiles para iniciar la cadena</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>eliminado</v>
+        <v>Suelta perfiles para iniciar la cadena</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Mover antes</v>
+        <v>eliminado</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Mover después</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Subir</v>
+        <v>Mover después</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Bajar</v>
+        <v>Subir</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intención de renderizado (todas)</v>
+        <v>Bajar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intención de renderizado para esta transformación</v>
+        <v>Intención de renderizado (todas)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
+        <v>Intención de renderizado para esta transformación</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
+        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
+        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Cadena</v>
+        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>No se pudo analizar la cadena.</v>
+        <v>Cadena</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Comprobando cadena…</v>
+        <v>No se pudo analizar la cadena.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>La cadena no conecta ({detail}).</v>
+        <v>Comprobando cadena…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
+        <v>La cadena no conecta ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Corrige la cadena antes de procesar imágenes</v>
+        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Borrar</v>
+        <v>Corrige la cadena antes de procesar imágenes</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nombre del DeviceLink</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Creando…</v>
+        <v>Nombre del DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
+        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Crea una cadena para procesar imágenes</v>
+        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
+        <v>Crea una cadena para procesar imágenes</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Imagen transformada guardada.</v>
+        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagen transformada guardada.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Archivo de datos demasiado grande.</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformar datos</v>
+        <v>Archivo de datos demasiado grande.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Transformando…</v>
+        <v>Transformar datos</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Preferir</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condición</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condición</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>media</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>parches</v>
+        <v>media</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} duplicados</v>
+        <v>parches</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Resultado de la transformación</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} parches</v>
+        <v>Resultado de la transformación</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
+        <v>{src} → {dst} · {n} parches</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Guardar como</v>
+        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Guardar</v>
+        <v>Guardar como</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Invertir transformación</v>
+        <v>Guardar</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Invirtiendo…</v>
+        <v>Invertir transformación</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Invertir</v>
+        <v>Invirtiendo…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>última etapa</v>
+        <v>Invertir</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>primera etapa</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Datos en {in} → buscar {out}</v>
+        <v>primera etapa</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
+        <v>Datos en {in} → buscar {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
+        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Coste ΔE</v>
+        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Esta imagen tiene un perfil ICC incrustado.</v>
+        <v>Coste ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extraer y añadir a la cadena</v>
+        <v>Esta imagen tiene un perfil ICC incrustado.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Extrayendo…</v>
+        <v>Extraer y añadir a la cadena</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Descartar</v>
+        <v>Extrayendo…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
+        <v>Descartar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Opciones de salida de imagen</v>
+        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Codificación</v>
+        <v>Opciones de salida de imagen</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Igual que el origen</v>
+        <v>Codificación</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bits</v>
+        <v>Igual que el origen</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flotante (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compresión</v>
+        <v>Flotante (32 bits)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Ninguna</v>
+        <v>Compresión</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planar</v>
+        <v>Ninguna</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Compuesto</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separado</v>
+        <v>Compuesto</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolación CMM</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolación CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Lineal</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Incrustar ICC</v>
+        <v>Lineal</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
+        <v>Incrustar ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Ensamblar TIFF espectral</v>
+        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
+        <v>Ensamblar TIFF espectral</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
+        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Ensamblar y guardar</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Ensamblando…</v>
+        <v>Ensamblar y guardar</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Se ensamblaron {n} canales.</v>
+        <v>Ensamblando…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
+        <v>Se ensamblaron {n} canales.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Cancelar</v>
+        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} archivo(s) no cargados</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
+        <v>{n} archivo(s) no cargados</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>Aceptar</v>
+        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Aceptar</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>o</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Elegir archivo</v>
+        <v>o</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Encabezado</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Etiquetas</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validación</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Análisis</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Propósito de representación</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% tinta</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* de salida (tono)</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* de salida (tono)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimetría de los extremos</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Los extremos del rango de reproducción del perfil: el blanco del soporte, el negro más oscuro que imprimirá, la tinta que cuesta ese negro y el punto en el que cada matiz alcanza su máxima saturación.</v>
+        <v>Colorimetría de los extremos</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>El punto blanco es el color con colorante cero — el soporte desnudo. El punto negro se obtiene pasando el negro del PCS (L*=0, a*=b*=0) por la tabla B2A seleccionada para obtener el entintado que el perfil elige para el negro, y leyendo después ese entintado a través de A2B1. La cobertura total de tinta (TAC) es la suma de ese entintado. La colorimetría absoluta muestra el color propio del soporte; la relativa lo refiere a un blanco perfecto.</v>
+        <v>Los extremos del rango de reproducción del perfil: el blanco del soporte, el negro más oscuro que imprimirá, la tinta que cuesta ese negro y el punto en el que cada matiz alcanza su máxima saturación.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativa</v>
+        <v>El punto blanco es el color con colorante cero — el soporte desnudo. El punto negro se obtiene pasando el negro del PCS (L*=0, a*=b*=0) por la tabla B2A seleccionada para obtener el entintado que el perfil elige para el negro, y leyendo después ese entintado a través de A2B1. La cobertura total de tinta (TAC) es la suma de ese entintado. La colorimetría absoluta muestra el color propio del soporte; la relativa lo refiere a un blanco perfecto.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absoluta</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Punto blanco</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Punto negro</v>
+        <v>Punto blanco</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Entintado en el punto negro</v>
+        <v>Punto negro</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Entintado en el punto negro</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Este perfil no tiene etiqueta de punto blanco del medio, por lo que la colorimetría absoluta no está disponible.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>La colorimetría de los extremos solo está disponible para perfiles de salida (impresora) — supone que colorante cero significa soporte desnudo.</v>
+        <v>Este perfil no tiene etiqueta de punto blanco del medio, por lo que la colorimetría absoluta no está disponible.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Tinta plena frente a croma máximo</v>
+        <v>La colorimetría de los extremos solo está disponible para perfiles de salida (impresora) — supone que colorante cero significa soporte desnudo.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Dónde queda cada vértice de tinta y el punto más cromático del camino hasta él. Medido a través de A2B1, por lo que estas filas no cambian con el propósito de representación de arriba. En un perfil bien formado ambas filas coinciden; si el croma máximo llega antes de la tinta plena, la tinta añadida más allá de ese punto solo oscurece.</v>
+        <v>Tinta plena frente a croma máximo</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Matiz</v>
+        <v>Dónde queda cada vértice de tinta y el punto más cromático del camino hasta él. Medido a través de A2B1, por lo que estas filas no cambian con el propósito de representación de arriba. En un perfil bien formado ambas filas coinciden; si el croma máximo llega antes de la tinta plena, la tinta añadida más allá de ese punto solo oscurece.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Tinta plena</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Con entintado</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>El croma máximo se alcanza antes de la tinta plena — la tinta más allá de este punto solo oscurece.</v>
+        <v>Con entintado</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Uso de tinta en las sombras</v>
+        <v>El croma máximo se alcanza antes de la tinta plena — la tinta más allá de este punto solo oscurece.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Cuatro trayectos rectos por el plano a*b* con una claridad constante y deliberadamente oscura, pasados por la tabla B2A seleccionada. Todas las muestras comparten la misma L*, así que cualquier salto brusco o inversión de un colorante procede únicamente del tratamiento del matiz y del croma — la firma de un artefacto de mapeo de gama en las sombras.</v>
+        <v>Uso de tinta en las sombras</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>El uso de tinta en las sombras solo está disponible para perfiles de salida (impresora).</v>
+        <v>Cuatro trayectos rectos por el plano a*b* con una claridad constante y deliberadamente oscura, pasados por la tabla B2A seleccionada. Todas las muestras comparten la misma L*, así que cualquier salto brusco o inversión de un colorante procede únicamente del tratamiento del matiz y del croma — la firma de un artefacto de mapeo de gama en las sombras.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plano de L* constante</v>
+        <v>El uso de tinta en las sombras solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>con compensación de punto negro desde</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Posición a lo largo del trayecto</v>
+        <v>con compensación de punto negro desde</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Trayecto</v>
+        <v>Posición a lo largo del trayecto</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Trayectorias de entintado primario por el neutro</v>
+        <v>Trayecto</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Tres trayectorias dentro de la gama — cian→rojo, magenta→verde, amarillo→azul — cada una a través del eje neutro en la claridad media de sus extremos, mediante la tabla B2A seleccionada. Cada muestra está dentro de la gama, así que a diferencia de las trayectorias de sombra, cualquier salto o inversión de un colorante es un defecto de suavidad de la CLUT y no un artefacto de mapeo de gama.</v>
+        <v>Trayectorias de entintado primario por el neutro</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Las trayectorias de entintado primario solo están disponibles para perfiles de salida (impresora).</v>
+        <v>Tres trayectorias dentro de la gama — cian→rojo, magenta→verde, amarillo→azul — cada una a través del eje neutro en la claridad media de sus extremos, mediante la tabla B2A seleccionada. Cada muestra está dentro de la gama, así que a diferencia de las trayectorias de sombra, cualquier salto o inversión de un colorante es un defecto de suavidad de la CLUT y no un artefacto de mapeo de gama.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Posición a lo largo de la trayectoria (neutro en el centro)</v>
+        <v>Las trayectorias de entintado primario solo están disponibles para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensación de punto negro aplicada para este propósito.</v>
+        <v>Posición a lo largo de la trayectoria (neutro en el centro)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Estadísticas de uso de tinta</v>
+        <v>Compensación de punto negro aplicada para este propósito.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Cuánto de cada colorante deposita el perfil, como suma y como proporción del total — la firma de consumo de tinta de la separación.</v>
+        <v>Estadísticas de uso de tinta</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Las estadísticas de uso de tinta solo están disponibles para perfiles de salida (impresora).</v>
+        <v>Cuánto de cada colorante deposita el perfil, como suma y como proporción del total — la firma de consumo de tinta de la separación.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Eje neutro</v>
+        <v>Las estadísticas de uso de tinta solo están disponibles para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Cobertura media</v>
+        <v>Eje neutro</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Proporción de tinta</v>
+        <v>Cobertura media</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>La proporción de tinta es la huella de la construcción del neutro — la fracción de cada colorante en el total de tinta depositada, independiente del número de muestras.</v>
+        <v>Proporción de tinta</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Puntos dentro de la gama</v>
+        <v>La proporción de tinta es la huella de la construcción del neutro — la fracción de cada colorante en el total de tinta depositada, independiente del número de muestras.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>El uso de tinta en todos los colores de la gama necesita el contorno de gama del lado B2A, aún no implementado — pendiente.</v>
+        <v>Puntos dentro de la gama</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>No hay datos de colorante para resumir.</v>
+        <v>El uso de tinta en todos los colores de la gama necesita el contorno de gama del lado B2A, aún no implementado — pendiente.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Seleccione una tabla B2A (PCS→dispositivo) abajo para ver también una imagen en escala de grises de la cobertura de tinta de cada colorante.</v>
+        <v>No hay datos de colorante para resumir.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Cobertura de tinta de cada colorante sobre la misma retícula (más oscuro = más tinta).</v>
+        <v>Seleccione una tabla B2A (PCS→dispositivo) abajo para ver también una imagen en escala de grises de la cobertura de tinta de cada colorante.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cian</v>
+        <v>Cobertura de tinta de cada colorante sobre la misma retícula (más oscuro = más tinta).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cian</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Amarillo</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rojo</v>
+        <v>Amarillo</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Verde</v>
+        <v>Rojo</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Azul</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Negro</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptual</v>
+        <v>Negro</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturación</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Propósito de representación</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE de ciclo</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>media</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analizando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Análisis</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Gráfico</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Salida bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Curvas de salida</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Imagen CLUT</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Imagen de gama</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Cromaticidad</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Tabla de la curva</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tablas</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Datos</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Evaluar</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Cargando…</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Entrada</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Salida</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Coma flotante</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalizado</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Legible</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Cargando…</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Seguridad</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformidad</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Calidad</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>Puntos de código</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>Curva de ganancia</v>
+        <v>Puntos de código</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>Entorno</v>
+        <v>Curva de ganancia</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>Mostrando el respaldo SDR</v>
+        <v>Entorno</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>Perfil HDR en la cadena</v>
+        <v>Mostrando el respaldo SDR</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Las transformaciones a través de un perfil HDR usan su AToB0Tag — la representación SDR fijada que exige la cláusula 8.10.6 — porque la cláusula 8.10.1 no le deja etiquetas TRC. El resultado es ese respaldo, no comportamiento HDR.</v>
+        <v>Perfil HDR en la cadena</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Son perfiles HDR, sin etiquetas TRC, por lo que el gamut se construye a partir del AToB0Tag: la representación SDR fijada que la cláusula 8.10.6 exige a los consumidores sin procesamiento HDR. No es el gamut HDR del perfil, que no puede dibujarse en un PCS acotado.</v>
+        <v>Las transformaciones a través de un perfil HDR usan su AToB0Tag — la representación SDR fijada que exige la cláusula 8.10.6 — porque la cláusula 8.10.1 no le deja etiquetas TRC. El resultado es ese respaldo, no comportamiento HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Detectando…</v>
+        <v>Son perfiles HDR, sin etiquetas TRC, por lo que el gamut se construye a partir del AToB0Tag: la representación SDR fijada que la cláusula 8.10.6 exige a los consumidores sin procesamiento HDR. No es el gamut HDR del perfil, que no puede dibujarse en un PCS acotado.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>No se pudo detectar el entorno.</v>
+        <v>Detectando…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>Pantalla HDR</v>
+        <v>No se pudo detectar el entorno.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>Gamut amplio</v>
+        <v>Pantalla HDR</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>Ruta de lienzo HDR</v>
+        <v>Gamut amplio</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>Ruta de lienzo HDR</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>ninguna</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>sí</v>
+        <v>ninguna</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>no</v>
+        <v>sí</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>no informado</v>
+        <v>no</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>Formato</v>
+        <v>no informado</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>Inspeccionar</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>Mostrar</v>
+        <v>Inspeccionar</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>Mostrar</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>Leer el perfil ICC incrustado: no requiere códec</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>Mostrar los píxeles</v>
+        <v>Leer el perfil ICC incrustado: no requiere códec</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>Representar más brillante que el blanco</v>
+        <v>Mostrar los píxeles</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>Decodificado por profiletool, por tanto independiente del navegador</v>
+        <v>Representar más brillante que el blanco</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>Este navegador no ha informado del margen HDR de la pantalla, solo de si existe una ruta HDR.</v>
+        <v>Decodificado por profiletool, por tanto independiente del navegador</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>Flags del navegador</v>
+        <v>Este navegador no ha informado del margen HDR de la pantalla, solo de si existe una ruta HDR.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>activado</v>
+        <v>Flags del navegador</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>no activado</v>
+        <v>activado</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>no se puede detectar aquí</v>
+        <v>no activado</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>Necesario para representar HDR en este navegador: sin WebGPU, el lienzo HDR es la única vía. La inspección de perfiles funciona sin él.</v>
+        <v>no se puede detectar aquí</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>Opcional: el HDR puede representarse con WebGPU, pero esto añade la vía de lienzo HDR y permite a profiletool leer el margen HDR real de la pantalla.</v>
+        <v>Necesario para representar HDR en este navegador: sin WebGPU, el lienzo HDR es la única vía. La inspección de perfiles funciona sin él.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>Las páginas web no pueden abrir páginas de flags. Pega esto en la barra de direcciones, elige Enabled y reinicia el navegador.</v>
+        <v>Opcional: el HDR puede representarse con WebGPU, pero esto añade la vía de lienzo HDR y permite a profiletool leer el margen HDR real de la pantalla.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>Copiar</v>
+        <v>Las páginas web no pueden abrir páginas de flags. Pega esto en la barra de direcciones, elige Enabled y reinicia el navegador.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>Copiado</v>
+        <v>Copiar</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>No se pudo copiar — selecciona la dirección y cópiala.</v>
+        <v>Copiado</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>Relación de píxeles</v>
+        <v>No se pudo copiar — selecciona la dirección y cópiala.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>Monitor actual</v>
+        <v>Relación de píxeles</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>sin nombre</v>
+        <v>Monitor actual</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>principal</v>
+        <v>sin nombre</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>integrado</v>
+        <v>principal</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>Margen HDR</v>
+        <v>integrado</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>no expuesto por este navegador</v>
+        <v>Margen HDR</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium lo informa en pasos: log₂ del brillo máximo de la pantalla ÷ su nivel de blanco SDR. En Windows solo se actualiza cuando Chrome vuelve a leer la pantalla —la ventana pasa a otra pantalla o Chrome vuelve a activarse—, no cuando cambia el brillo.</v>
+        <v>no expuesto por este navegador</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} pasos (≈{ratio}× el blanco SDR)</v>
+        <v>Chromium lo informa en pasos: log₂ del brillo máximo de la pantalla ÷ su nivel de blanco SDR. En Windows solo se actualiza cuando Chrome vuelve a leer la pantalla —la ventana pasa a otra pantalla o Chrome vuelve a activarse—, no cuando cambia el brillo.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} pasos (≈{ratio}× el blanco SDR)</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>Ganancia a un margen de pantalla</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>Ve una imagen HDR en esta pantalla. Los archivos que el navegador sabe decodificar los muestra el propio navegador; OpenEXR y Radiance HDR los decodifica y representa profiletool.</v>
+        <v>Ganancia a un margen de pantalla</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>Suelta aquí una imagen HDR o haz clic para elegir una</v>
+        <v>Ve una imagen HDR en esta pantalla. Los archivos que el navegador sabe decodificar los muestra el propio navegador; OpenEXR y Radiance HDR los decodifica y representa profiletool.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluido JPEG con gain map), PNG — y HEIC y JPEG XL en Safari.</v>
+        <v>Suelta aquí una imagen HDR o haz clic para elegir una</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>Elegir otra</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluido JPEG con gain map), PNG — y HEIC y JPEG XL en Safari.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>Borrar</v>
+        <v>Elegir otra</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>Perfil ICC incrustado</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>ninguno — OpenEXR indica el color mediante cromaticidades</v>
+        <v>Perfil ICC incrustado</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>ninguno — Radiance HDR indica el color mediante su cabecera PRIMARIES</v>
+        <v>ninguno — OpenEXR indica el color mediante cromaticidades</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>comprobando…</v>
+        <v>ninguno — Radiance HDR indica el color mediante su cabecera PRIMARIES</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>ninguno</v>
+        <v>comprobando…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>Abrir en la pestaña Perfil</v>
+        <v>ninguno</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>Mapa de ganancia</v>
+        <v>Abrir en la pestaña Perfil</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>detectado, no decodificado</v>
+        <v>Mapa de ganancia</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>Eso no es una imagen. Carga los perfiles desde el panel Perfiles.</v>
+        <v>detectado, no decodificado</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>No es un formato de imagen que profiletool reconozca.</v>
+        <v>Eso no es una imagen. Carga los perfiles desde el panel Perfiles.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>Los píxeles TIFF aún no se muestran aquí: los navegadores no decodifican TIFF y aún no está decidido cómo se codifica el HDR en un TIFF de 16 bits (fase 4.3). Su perfil incrustado se puede inspeccionar.</v>
+        <v>No es un formato de imagen que profiletool reconozca.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>No se puede mostrar esta imagen aquí:</v>
+        <v>Los píxeles TIFF aún no se muestran aquí: los navegadores no decodifican TIFF y aún no está decidido cómo se codifica el HDR en un TIFF de 16 bits (fase 4.3). Su perfil incrustado se puede inspeccionar.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>Su perfil incrustado aún se puede inspeccionar.</v>
+        <v>No se puede mostrar esta imagen aquí:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>Mostrado por</v>
+        <v>Su perfil incrustado aún se puede inspeccionar.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>el navegador</v>
+        <v>Mostrado por</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>el navegador</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>Pantalla HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>Los navegadores ignoran el HDR indicado solo por un perfil ICC incrustado, así que esta imagen puede verse apagada y plana.</v>
+        <v>Pantalla HDR</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>Este navegador no puede cambiar una imagen entre SDR y HDR, así que se muestra tal como la representa.</v>
+        <v>Los navegadores ignoran el HDR indicado solo por un perfil ICC incrustado, así que esta imagen puede verse apagada y plana.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>El navegador no pudo decodificar esta imagen.</v>
+        <v>Este navegador no puede cambiar una imagen entre SDR y HDR, así que se muestra tal como la representa.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>Salida</v>
+        <v>El navegador no pudo decodificar esta imagen.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>Lienzo HDR (float16)</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU (rango extendido)</v>
+        <v>Lienzo HDR (float16)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>Lienzo SDR (con tone mapping)</v>
+        <v>WebGPU (rango extendido)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>Tamaño</v>
+        <v>Lienzo SDR (con tone mapping)</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>Píxel más brillante</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>{n}× el blanco SDR</v>
+        <v>Píxel más brillante</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>Cromaticidades</v>
+        <v>{n}× el blanco SDR</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>no indicadas — se asume Rec. 709</v>
+        <v>Cromaticidades</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from} no está disponible aquí ({why}); se usa la siguiente salida.</v>
+        <v>no indicadas — se asume Rec. 709</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>Esta salida no puede transportar valores más brillantes que el blanco, así que se muestra la representación SDR con tone mapping.</v>
+        <v>{from} no está disponible aquí ({why}); se usa la siguiente salida.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>Exposición</v>
+        <v>Esta salida no puede transportar valores más brillantes que el blanco, así que se muestra la representación SDR con tone mapping.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} pasos</v>
+        <v>Exposición</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>No se pudo decodificar:</v>
+        <v>{n} pasos</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>Este archivo ocupa {size} MB; la pestaña HDR abre imágenes de hasta {max} MB.</v>
+        <v>No se pudo decodificar:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>No se pudo aplicar el perfil:</v>
+        <v>Este archivo ocupa {size} MB; la pestaña HDR abre imágenes de hasta {max} MB.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>No se pudo dibujar la imagen:</v>
+        <v>No se pudo aplicar el perfil:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>(estos primarios no definen un espacio de color — se ignoran y se usa Rec. 709)</v>
+        <v>No se pudo dibujar la imagen:</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>el perfil de un JPEG XL está comprimido dentro del codestream, que profiletool aún no descomprime</v>
+        <v>(estos primarios no definen un espacio de color — se ignoran y se usa Rec. 709)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>Decodificando…</v>
+        <v>el perfil de un JPEG XL está comprimido dentro del codestream, que profiletool aún no descomprime</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>Rango dinámico</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>Este navegador solo ofrece los dos extremos, no una mezcla.</v>
+        <v>Rango dinámico</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>decodificado por el propio profiletool, así que no depende del navegador</v>
+        <v>Este navegador solo ofrece los dos extremos, no una mezcla.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>este navegador lo decodifica</v>
+        <v>decodificado por el propio profiletool, así que no depende del navegador</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>este navegador no lo decodifica</v>
+        <v>este navegador lo decodifica</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>mostrar HEIC requiere Safari u otro navegador WebKit — Chrome y Firefox no decodifican HEIC en ninguna plataforma, incluido macOS</v>
+        <v>este navegador no lo decodifica</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>mostrar JPEG XL requiere Safari; los demás navegadores aún no lo admiten</v>
+        <v>mostrar HEIC requiere Safari u otro navegador WebKit — Chrome y Firefox no decodifican HEIC en ninguna plataforma, incluido macOS</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>aplazado a una versión posterior</v>
+        <v>mostrar JPEG XL requiere Safari; los demás navegadores aún no lo admiten</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>esta pantalla no informa de ninguna ruta HDR, así que el HDR se muestra en SDR con tone mapping</v>
+        <v>aplazado a una versión posterior</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>este navegador no ofrece un lienzo HDR (requiere lienzo float16 o WebGPU)</v>
+        <v>esta pantalla no informa de ninguna ruta HDR, así que el HDR se muestra en SDR con tone mapping</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox no muestra imágenes HDR ni lee gain maps; el contenido HDR se muestra en SDR</v>
+        <v>este navegador no ofrece un lienzo HDR (requiere lienzo float16 o WebGPU)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>la inspección solo necesita analizar el contenedor, no un códec</v>
+        <v>Firefox no muestra imágenes HDR ni lee gain maps; el contenido HDR se muestra en SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>hay pantalla HDR y lienzo HDR disponibles</v>
+        <v>la inspección solo necesita analizar el contenedor, no un códec</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>formato desconocido</v>
+        <v>hay pantalla HDR y lienzo HDR disponibles</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{browser} en {os}</v>
+        <v>formato desconocido</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · pantalla HDR detectada</v>
+        <v>{browser} en {os}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · pantalla SDR</v>
+        <v>{name} · pantalla HDR detectada</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU aplicó el tone mapping «{mode}», así que la salida se limita a SDR</v>
+        <v>{name} · pantalla SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>Este navegador no informa del tone mapping de WebGPU aplicado, así que la salida HDR no está confirmada</v>
+        <v>WebGPU aplicó el tone mapping «{mode}», así que la salida se limita a SDR</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>Pico de la pantalla</v>
+        <v>Este navegador no informa del tone mapping de WebGPU aplicado, así que la salida HDR no está confirmada</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>{r}× el blanco SDR ({n} pasos)</v>
+        <v>Pico de la pantalla</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× — pantalla SDR</v>
+        <v>{r}× el blanco SDR ({n} pasos)</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>desconocido</v>
+        <v>1× — pantalla SDR</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>Esta pantalla no informa de HDR, así que el navegador muestra la imagen en SDR en ambos extremos.</v>
+        <v>desconocido</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>Esta pantalla no informa de HDR, así que todo lo más brillante que el blanco SDR se recorta. «Ajustar a la pantalla» muestra en su lugar la representación con tone mapping.</v>
+        <v>Esta pantalla no informa de HDR, así que el navegador muestra la imagen en SDR en ambos extremos.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>Esta imagen pide {img}× el blanco SDR, pero esta pantalla solo llega a {disp}×, así que los valores más brillantes se recortan. «Ajustar a la pantalla» los atenúa hacia el pico de la pantalla.</v>
+        <v>Esta pantalla no informa de HDR, así que todo lo más brillante que el blanco SDR se recorta. «Ajustar a la pantalla» muestra en su lugar la representación con tone mapping.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>Ajustar a la pantalla</v>
+        <v>Esta imagen pide {img}× el blanco SDR, pero esta pantalla solo llega a {disp}×, así que los valores más brillantes se recortan. «Ajustar a la pantalla» los atenúa hacia el pico de la pantalla.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>Detalles de la imagen</v>
+        <v>Ajustar a la pantalla</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>no disponible — el navegador representa esta imagen y no puede limitarla a un pico dado</v>
+        <v>Detalles de la imagen</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>no disponible — esta salida no muestra nada por encima del blanco SDR</v>
+        <v>no disponible — el navegador representa esta imagen y no puede limitarla a un pico dado</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>no disponible — no se conoce el pico de esta pantalla</v>
+        <v>no disponible — esta salida no muestra nada por encima del blanco SDR</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>Acercar</v>
+        <v>no disponible — no se conoce el pico de esta pantalla</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>Alejar</v>
+        <v>Acercar</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>Ajustar imagen</v>
+        <v>Alejar</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>Píxeles reales (1:1)</v>
+        <v>Ajustar imagen</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>Arrastra para desplazar · Ctrl+rueda para hacer zoom · doble clic para restablecer</v>
+        <v>Píxeles reales (1:1)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>Arrastra para cambiar el tamaño del área de imagen; doble clic para volver al tamaño predeterminado</v>
+        <v>Arrastra para desplazar · Ctrl+rueda para hacer zoom · doble clic para restablecer</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>Vista de la imagen</v>
+        <v>Arrastra para cambiar el tamaño del área de imagen; doble clic para volver al tamaño predeterminado</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
+        <v>Vista de la imagen</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>sin límite</v>
+        <v>Limita el brillo al pico que informa esta pantalla. En Windows ese valor puede ir por detrás de los cambios de brillo.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>límite {n} pasos ({r}×)</v>
+        <v>sin límite</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>Blanco SDR</v>
+        <v>límite {n} pasos ({r}×)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
+        <v>Blanco SDR</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>Parche blanco SDR</v>
+        <v>Blanco SDR simple, para comparar. En una pantalla HDR, las luces altas HDR se ven más brillantes que este.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
+        <v>Parche blanco SDR</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>Asignar perfil</v>
+        <v>Arrástralo para moverlo; haz doble clic para volver a colocarlo junto a la imagen.</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>Ninguno — según indique el archivo</v>
+        <v>Asignar perfil</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>Perfil incrustado ({n} B)</v>
+        <v>Ninguno — según indique el archivo</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>Perfiles HDR del pool</v>
+        <v>Perfil incrustado ({n} B)</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>Perfil</v>
+        <v>Perfiles HDR del pool</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>perfil incrustado</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>Ruta del motor de color</v>
+        <v>perfil incrustado</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>Ruta HDR, curva de ganancia aplicada</v>
+        <v>Ruta del motor de color</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>Ruta HDR, sin curva de ganancia</v>
+        <v>Ruta HDR, curva de ganancia aplicada</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>AToB0 precalculado — no es la ruta HDR</v>
+        <v>Ruta HDR, sin curva de ganancia</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>Transferencia</v>
+        <v>AToB0 precalculado — no es la ruta HDR</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>Blanco de referencia HDR</v>
+        <v>Transferencia</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Valores lineales</v>
+        <v>Blanco de referencia HDR</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>Archivo 1,0 = blanco de referencia HDR</v>
+        <v>Valores lineales</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>Archivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>Archivo 1,0 = blanco de referencia HDR</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Los archivos OpenEXR y Radiance HDR sitúan por convención el blanco SDR en 1,0, mientras que una transferencia ICC lineal lee 1,0 como 1 cd/m². De forma predeterminada, el archivo se escala para que su 1,0 caiga en el blanco de referencia HDR del perfil.</v>
+        <v>Archivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>Escala de entrada</v>
+        <v>Los archivos OpenEXR y Radiance HDR sitúan por convención el blanco SDR en 1,0, mientras que una transferencia ICC lineal lee 1,0 como 1 cd/m². De forma predeterminada, el archivo se escala para que su 1,0 caiga en el blanco de referencia HDR del perfil.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} — archivo 1,0 = blanco de referencia</v>
+        <v>Escala de entrada</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>ninguna — archivo 1,0 = 1 cd/m²</v>
+        <v>×{w} — archivo 1,0 = blanco de referencia</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>Margen objetivo</v>
+        <v>ninguna — archivo 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>{r}× el blanco de referencia ({n} pasos)</v>
+        <v>Margen objetivo</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Mapeo de tonos</v>
+        <v>{r}× el blanco de referencia ({n} pasos)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>Auto (orden de la cláusula 8.10.3)</v>
+        <v>Mapeo de tonos</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Curva de ganancia (HAGC)</v>
+        <v>Auto (orden de la cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>Alternativa SDR precalculada (AToB0)</v>
+        <v>Curva de ganancia (HAGC)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>Desactivado — como un CMM anterior a la enmienda</v>
+        <v>Alternativa SDR precalculada (AToB0)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>Aplicando el perfil…</v>
+        <v>Desactivado — como un CMM anterior a la enmienda</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
+        <v>Aplicando el perfil…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
+        <v>{format} contiene luz lineal, así que necesita un perfil con transferencia Linear (8).</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
+        <v>Asignar un perfil requiere una imagen RGB de 3 canales.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>Perfiles HDR</v>
+        <v>Para interpretar sus valores, asigna un perfil arriba.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Transferencia lineal</v>
+        <v>Perfiles HDR</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>Transferencia no lineal (PQ, HLG)</v>
+        <v>Transferencia lineal</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>Perfiles HDR — transferencia lineal</v>
+        <v>Transferencia no lineal (PQ, HLG)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Perfiles HDR — transferencia PQ / HLG</v>
+        <v>Perfiles HDR — transferencia lineal</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
+        <v>Perfiles HDR — transferencia PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
+        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
+        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>Margen de la pantalla</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>Base</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>Vista previa a través del motor de color</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
+        <v>Vista previa a través del motor de color</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>Mapeado para {h} pasos</v>
+        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
+        <v>Mapeado para {h} pasos</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>blanco de referencia</v>
+        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>pico de la pantalla</v>
+        <v>blanco de referencia</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>Vista previa no disponible: {why}</v>
+        <v>pico de la pantalla</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>el motor de color no tomó la ruta HDR para este perfil</v>
+        <v>Vista previa no disponible: {why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>Ganancia en todos los márgenes</v>
+        <v>el motor de color no tomó la ruta HDR para este perfil</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
+        <v>Ganancia en todos los márgenes</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
+        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>Margen de la pantalla (pasos)</v>
+        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Ganancia (pasos)</v>
+        <v>Margen de la pantalla (pasos)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Curva de la etiqueta</v>
+        <v>Ganancia (pasos)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>Base</v>
+        <v>Curva de la etiqueta</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>Control</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>Entrada = pico de la pantalla</v>
+        <v>Control</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>Curvas tonales de gris por margen</v>
+        <v>Entrada = pico de la pantalla</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
+        <v>Curvas tonales de gris por margen</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
+        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} pasos</v>
+        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} pasos (base)</v>
+        <v>{h} pasos</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>A {h} pasos (control)</v>
+        <v>{h} pasos (base)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>A {h} pasos (control)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Sin cambios</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>Identificar pantallas</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>Eventos de pantalla</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>Primarios de color</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>Características de transferencia</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>Rango completo</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>Rango reducido</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>INFORME</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>Correo electrónico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>(opcional)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>Cancelar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>Suscribirse</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>Cerrar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Error:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,2949 +1197,2957 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Ordenar por nombre</v>
+        <v>Toca para seleccionar y luego toca una pestaña para enviar.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nombre</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Nuevo perfil desde .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se abre; no se descarga nada hasta que pulses Guardar perfil ICC.</v>
+        <v>Nuevo perfil desde .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Elegir archivo .cube</v>
+        <v>Crea un DeviceLink ICC a partir de una LUT 3D .cube de Adobe/Resolve. El resultado se añade a tu conjunto y se abre; no se descarga nada hasta que pulses Guardar perfil ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Elegir archivo .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>o suéltalo aquí, o pega debajo</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Creando…</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Perfil</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Enlazar</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Espectral</v>
+        <v>Enlazar</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Arrastra perfiles del conjunto a esta pestaña</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Quitar</v>
+        <v>Arrastra perfiles del conjunto a esta pestaña</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Ningún perfil seleccionado</v>
+        <v>Quitar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
+        <v>Ningún perfil seleccionado</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Aún no hay nada que comparar</v>
+        <v>Arrastra un perfil del conjunto a la pestaña Perfil para inspeccionarlo.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
+        <v>Aún no hay nada que comparar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Comparación de gama</v>
+        <v>Arrastra uno o más perfiles a la pestaña Comparar.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
+        <v>Comparación de gama</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Propósito de representación</v>
+        <v>Las vistas de gama 3D y corte 2D llegarán aquí. Acumulados:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Envoltura</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Malla</v>
+        <v>Envoltura</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Números de eje</v>
+        <v>Malla</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacidad</v>
+        <v>Números de eje</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Color</v>
+        <v>Opacidad</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Sólido</v>
+        <v>Color</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Por tono</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotación</v>
+        <v>Por tono</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Plataforma giratoria</v>
+        <v>Rotación</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Órbita</v>
+        <v>Plataforma giratoria</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocidad de arrastre</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Alabeo</v>
+        <v>Velocidad de arrastre</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Velocidad de alabeo</v>
+        <v>Alabeo</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Construyendo la gama…</v>
+        <v>Velocidad de alabeo</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>sin gama</v>
+        <v>Construyendo la gama…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sin gama</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Envoltura de gama 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Corte de gama 2D</v>
+        <v>Envoltura de gama 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plano</v>
+        <v>Corte de gama 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Enlace</v>
+        <v>Ninguno de los perfiles seleccionados tiene una transformación dispositivo→PCS de la que derivar una gama.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
+        <v>Enlace</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
+        <v>La producción de DeviceLink y las transformaciones multiperfil llegarán en una fase posterior.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Creador de pantalla V4</v>
+        <v>Aquí llegarán más creadores de enlaces (DeviceLink, …).</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
+        <v>Creador de pantalla V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Pantalla RGB V5</v>
+        <v>Arrastra aquí un perfil de pantalla RGB V5 y un perfil de observador V5 para crear un perfil de pantalla V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>suelta un perfil de pantalla</v>
+        <v>Pantalla RGB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>suelta un perfil de pantalla</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>suelta un perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
+        <v>suelta un perfil de observador</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Crear perfil de pantalla V4</v>
+        <v>Se ignoró un perfil que no es ni una pantalla RGB V5 ni un observador.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nombre del perfil</v>
+        <v>Crear perfil de pantalla V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Crear</v>
+        <v>Nombre del perfil</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Creando…</v>
+        <v>Crear</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Flujo de enlace</v>
+        <v>«{name}» creado — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
+        <v>Flujo de enlace</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Hecho</v>
+        <v>Cree una cadena de perfiles y luego cree un DeviceLink, transforme una imagen o transforme un conjunto de datos de color a través de ella.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
+        <v>Hecho</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Comprobando imagen…</v>
+        <v>Suelta una imagen para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
+        <v>Comprobando imagen…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
+        <v>Imagen no compatible (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformar imagen</v>
+        <v>Imagen demasiado grande ({mp} MP; límite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Transformando…</v>
+        <v>Transformar imagen</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Suelta perfiles para iniciar la cadena</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>eliminado</v>
+        <v>Suelta perfiles para iniciar la cadena</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Mover antes</v>
+        <v>eliminado</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Mover después</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Subir</v>
+        <v>Mover después</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Bajar</v>
+        <v>Subir</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intención de renderizado (todas)</v>
+        <v>Bajar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intención de renderizado para esta transformación</v>
+        <v>Intención de renderizado (todas)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
+        <v>Intención de renderizado para esta transformación</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
+        <v>Las transformaciones usan diferentes intenciones de renderizado</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
+        <v>Invertir dirección de la cadena (invierte la transformación inicial y se propaga por toda la cadena)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Cadena</v>
+        <v>Se eliminó un perfil encadenado del conjunto — elimínalo para continuar.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>No se pudo analizar la cadena.</v>
+        <v>Cadena</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Comprobando cadena…</v>
+        <v>No se pudo analizar la cadena.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>La cadena no conecta ({detail}).</v>
+        <v>Comprobando cadena…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
+        <v>La cadena no conecta ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Corrige la cadena antes de procesar imágenes</v>
+        <v>El perfil {n} no conecta con la etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Borrar</v>
+        <v>Corrige la cadena antes de procesar imágenes</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Crear DeviceLink</v>
+        <v>Borrar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nombre del DeviceLink</v>
+        <v>Crear DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Creando…</v>
+        <v>Nombre del DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
+        <v>Creando…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
+        <v>Se creó «{name}» — añadido al conjunto y a esta pestaña.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Crea una cadena para procesar imágenes</v>
+        <v>Suelta imágenes {src} para convertirlas a {dst} — los resultados se descargan, no se almacena nada.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
+        <v>Crea una cadena para procesar imágenes</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Imagen transformada guardada.</v>
+        <v>Esta cadena no empieza ni termina en un espacio de color de imagen</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagen transformada guardada.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>No se pudo leer ese archivo.</v>
+        <v>Suelta un conjunto de datos de color (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Archivo de datos demasiado grande.</v>
+        <v>No se pudo leer ese archivo.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformar datos</v>
+        <v>Archivo de datos demasiado grande.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Transformando…</v>
+        <v>Transformar datos</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Preferir</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condición</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condición</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>media</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>parches</v>
+        <v>media</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} duplicados</v>
+        <v>parches</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Resultado de la transformación</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} parches</v>
+        <v>Resultado de la transformación</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
+        <v>{src} → {dst} · {n} parches</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Guardar como</v>
+        <v>Mostrando los primeros {shown} de {total} — Guardar los escribe todos.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Guardar</v>
+        <v>Guardar como</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Invertir transformación</v>
+        <v>Guardar</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Invirtiendo…</v>
+        <v>Invertir transformación</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Invertir</v>
+        <v>Invirtiendo…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>última etapa</v>
+        <v>Invertir</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>primera etapa</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Datos en {in} → buscar {out}</v>
+        <v>primera etapa</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
+        <v>Datos en {in} → buscar {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
+        <v>Invertir necesita una cadena de 2 a 3 perfiles</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Coste ΔE</v>
+        <v>El conjunto de datos debe estar en {in}; la búsqueda inversa produce {out} más un coste de invertibilidad por parche.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Esta imagen tiene un perfil ICC incrustado.</v>
+        <v>Coste ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extraer y añadir a la cadena</v>
+        <v>Esta imagen tiene un perfil ICC incrustado.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Extrayendo…</v>
+        <v>Extraer y añadir a la cadena</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Descartar</v>
+        <v>Extrayendo…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
+        <v>Descartar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Opciones de salida de imagen</v>
+        <v>Se extrajo el perfil incrustado — añadido al conjunto y colocado primero en la cadena.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Codificación</v>
+        <v>Opciones de salida de imagen</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Igual que el origen</v>
+        <v>Codificación</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bits</v>
+        <v>Igual que el origen</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flotante (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compresión</v>
+        <v>Flotante (32 bits)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Ninguna</v>
+        <v>Compresión</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planar</v>
+        <v>Ninguna</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Compuesto</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separado</v>
+        <v>Compuesto</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolación CMM</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolación CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Lineal</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Incrustar ICC</v>
+        <v>Lineal</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
+        <v>Incrustar ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Ensamblar TIFF espectral</v>
+        <v>La codificación, la compresión y el formato planar determinan el TIFF guardado. La salida RGB/Gray permanece en PNG a menos que se establezca una opción exclusiva de TIFF (flotante, LZW/ZIP, separado).</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
+        <v>Ensamblar TIFF espectral</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
+        <v>Suelta imágenes espectrales de un solo canal en el orden de los canales y luego ensámblalas en un único TIFF multicanal.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Suelta imágenes espectrales aquí (o haz clic para elegir)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Ensamblar y guardar</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Ensamblando…</v>
+        <v>Ensamblar y guardar</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Se ensamblaron {n} canales.</v>
+        <v>Ensamblando…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
+        <v>Se ensamblaron {n} canales.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Cancelar</v>
+        <v>Ninguno de esos parece ser una imagen (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} archivo(s) no cargados</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
+        <v>{n} archivo(s) no cargados</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>Aceptar</v>
+        <v>Estos archivos no son perfiles ICC, por lo que no se añadieron al conjunto:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Suelta un perfil ICC aquí</v>
+        <v>Aceptar</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>o</v>
+        <v>Suelta un perfil ICC aquí</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Elegir archivo</v>
+        <v>o</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>Archivos .icc y .icm</v>
+        <v>Elegir archivo</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Encabezado</v>
+        <v>Archivos .icc y .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Etiquetas</v>
+        <v>Encabezado</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validación</v>
+        <v>Etiquetas</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Análisis</v>
+        <v>Validación</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Entintado del eje neutro</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
+        <v>Entintado del eje neutro</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
+        <v>Colorante depositado a lo largo del eje neutro (a*=b*=0) a medida que la claridad pasa de blanco (L*=100) a negro (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
+        <v>El entintado del eje neutro solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Propósito de representación</v>
+        <v>Este perfil no tiene una tabla B2A (PCS→dispositivo) que muestrear.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% tinta</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* de salida (tono)</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* de salida (tono)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimetría de los extremos</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Los extremos del rango de reproducción del perfil: el blanco del soporte, el negro más oscuro que imprimirá, la tinta que cuesta ese negro y el punto en el que cada matiz alcanza su máxima saturación.</v>
+        <v>Colorimetría de los extremos</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>El punto blanco es el color con colorante cero — el soporte desnudo. El punto negro se obtiene pasando el negro del PCS (L*=0, a*=b*=0) por la tabla B2A seleccionada para obtener el entintado que el perfil elige para el negro, y leyendo después ese entintado a través de A2B1. La cobertura total de tinta (TAC) es la suma de ese entintado. La colorimetría absoluta muestra el color propio del soporte; la relativa lo refiere a un blanco perfecto.</v>
+        <v>Los extremos del rango de reproducción del perfil: el blanco del soporte, el negro más oscuro que imprimirá, la tinta que cuesta ese negro y el punto en el que cada matiz alcanza su máxima saturación.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativa</v>
+        <v>El punto blanco es el color con colorante cero — el soporte desnudo. El punto negro se obtiene pasando el negro del PCS (L*=0, a*=b*=0) por la tabla B2A seleccionada para obtener el entintado que el perfil elige para el negro, y leyendo después ese entintado a través de A2B1. La cobertura total de tinta (TAC) es la suma de ese entintado. La colorimetría absoluta muestra el color propio del soporte; la relativa lo refiere a un blanco perfecto.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absoluta</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Punto blanco</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Punto negro</v>
+        <v>Punto blanco</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Entintado en el punto negro</v>
+        <v>Punto negro</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Entintado en el punto negro</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Este perfil no tiene etiqueta de punto blanco del medio, por lo que la colorimetría absoluta no está disponible.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>La colorimetría de los extremos solo está disponible para perfiles de salida (impresora) — supone que colorante cero significa soporte desnudo.</v>
+        <v>Este perfil no tiene etiqueta de punto blanco del medio, por lo que la colorimetría absoluta no está disponible.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Tinta plena frente a croma máximo</v>
+        <v>La colorimetría de los extremos solo está disponible para perfiles de salida (impresora) — supone que colorante cero significa soporte desnudo.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Dónde queda cada vértice de tinta y el punto más cromático del camino hasta él. Medido a través de A2B1, por lo que estas filas no cambian con el propósito de representación de arriba. En un perfil bien formado ambas filas coinciden; si el croma máximo llega antes de la tinta plena, la tinta añadida más allá de ese punto solo oscurece.</v>
+        <v>Tinta plena frente a croma máximo</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Matiz</v>
+        <v>Dónde queda cada vértice de tinta y el punto más cromático del camino hasta él. Medido a través de A2B1, por lo que estas filas no cambian con el propósito de representación de arriba. En un perfil bien formado ambas filas coinciden; si el croma máximo llega antes de la tinta plena, la tinta añadida más allá de ese punto solo oscurece.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Tinta plena</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Con entintado</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>El croma máximo se alcanza antes de la tinta plena — la tinta más allá de este punto solo oscurece.</v>
+        <v>Con entintado</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Uso de tinta en las sombras</v>
+        <v>El croma máximo se alcanza antes de la tinta plena — la tinta más allá de este punto solo oscurece.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Cuatro trayectos rectos por el plano a*b* con una claridad constante y deliberadamente oscura, pasados por la tabla B2A seleccionada. Todas las muestras comparten la misma L*, así que cualquier salto brusco o inversión de un colorante procede únicamente del tratamiento del matiz y del croma — la firma de un artefacto de mapeo de gama en las sombras.</v>
+        <v>Uso de tinta en las sombras</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>El uso de tinta en las sombras solo está disponible para perfiles de salida (impresora).</v>
+        <v>Cuatro trayectos rectos por el plano a*b* con una claridad constante y deliberadamente oscura, pasados por la tabla B2A seleccionada. Todas las muestras comparten la misma L*, así que cualquier salto brusco o inversión de un colorante procede únicamente del tratamiento del matiz y del croma — la firma de un artefacto de mapeo de gama en las sombras.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plano de L* constante</v>
+        <v>El uso de tinta en las sombras solo está disponible para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>con compensación de punto negro desde</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Posición a lo largo del trayecto</v>
+        <v>con compensación de punto negro desde</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Trayecto</v>
+        <v>Posición a lo largo del trayecto</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Trayectorias de entintado primario por el neutro</v>
+        <v>Trayecto</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Tres trayectorias dentro de la gama — cian→rojo, magenta→verde, amarillo→azul — cada una a través del eje neutro en la claridad media de sus extremos, mediante la tabla B2A seleccionada. Cada muestra está dentro de la gama, así que a diferencia de las trayectorias de sombra, cualquier salto o inversión de un colorante es un defecto de suavidad de la CLUT y no un artefacto de mapeo de gama.</v>
+        <v>Trayectorias de entintado primario por el neutro</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Las trayectorias de entintado primario solo están disponibles para perfiles de salida (impresora).</v>
+        <v>Tres trayectorias dentro de la gama — cian→rojo, magenta→verde, amarillo→azul — cada una a través del eje neutro en la claridad media de sus extremos, mediante la tabla B2A seleccionada. Cada muestra está dentro de la gama, así que a diferencia de las trayectorias de sombra, cualquier salto o inversión de un colorante es un defecto de suavidad de la CLUT y no un artefacto de mapeo de gama.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Posición a lo largo de la trayectoria (neutro en el centro)</v>
+        <v>Las trayectorias de entintado primario solo están disponibles para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensación de punto negro aplicada para este propósito.</v>
+        <v>Posición a lo largo de la trayectoria (neutro en el centro)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Estadísticas de uso de tinta</v>
+        <v>Compensación de punto negro aplicada para este propósito.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Cuánto de cada colorante deposita el perfil, como suma y como proporción del total — la firma de consumo de tinta de la separación.</v>
+        <v>Estadísticas de uso de tinta</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Las estadísticas de uso de tinta solo están disponibles para perfiles de salida (impresora).</v>
+        <v>Cuánto de cada colorante deposita el perfil, como suma y como proporción del total — la firma de consumo de tinta de la separación.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Eje neutro</v>
+        <v>Las estadísticas de uso de tinta solo están disponibles para perfiles de salida (impresora).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Cobertura media</v>
+        <v>Eje neutro</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Proporción de tinta</v>
+        <v>Cobertura media</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>La proporción de tinta es la huella de la construcción del neutro — la fracción de cada colorante en el total de tinta depositada, independiente del número de muestras.</v>
+        <v>Proporción de tinta</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Puntos dentro de la gama</v>
+        <v>La proporción de tinta es la huella de la construcción del neutro — la fracción de cada colorante en el total de tinta depositada, independiente del número de muestras.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>El uso de tinta en todos los colores de la gama necesita el contorno de gama del lado B2A, aún no implementado — pendiente.</v>
+        <v>Puntos dentro de la gama</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>No hay datos de colorante para resumir.</v>
+        <v>El uso de tinta en todos los colores de la gama necesita el contorno de gama del lado B2A, aún no implementado — pendiente.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Seleccione una tabla B2A (PCS→dispositivo) abajo para ver también una imagen en escala de grises de la cobertura de tinta de cada colorante.</v>
+        <v>No hay datos de colorante para resumir.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Cobertura de tinta de cada colorante sobre la misma retícula (más oscuro = más tinta).</v>
+        <v>Seleccione una tabla B2A (PCS→dispositivo) abajo para ver también una imagen en escala de grises de la cobertura de tinta de cada colorante.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cian</v>
+        <v>Cobertura de tinta de cada colorante sobre la misma retícula (más oscuro = más tinta).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cian</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Amarillo</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rojo</v>
+        <v>Amarillo</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Verde</v>
+        <v>Rojo</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Azul</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Negro</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptual</v>
+        <v>Negro</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturación</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturación</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Estadísticas del perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
+        <v>Estadísticas del perfil</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
+        <v>Métricas de todo el perfil por propósito de representación: el volumen de gama delimitado por la transformación dispositivo→PCS (ΔE*ab³) y la precisión del ciclo B2A — ΔE*ab de un recorrido Lab → dispositivo → Lab a través del perfil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Propósito de representación</v>
+        <v>Este perfil no tiene CLUT dispositivo↔PCS — las estadísticas del perfil no se aplican (p. ej. un perfil de pantalla matriz/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volumen de gama (ΔE³)</v>
+        <v>Propósito de representación</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE de ciclo</v>
+        <v>Volumen de gama (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
+        <v>ΔE de ciclo</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>media</v>
+        <v>El contorno de la gama se colapsó o quedó mayormente indefinido, por lo que este volumen de gama no es fiable.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analizando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Análisis</v>
+        <v>Analizando…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
+        <v>Análisis</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Gráfico</v>
+        <v>Análisis de calidad de todo el perfil, derivados de la transformación dispositivo→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Salida bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Salida bruta</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Curvas de salida</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Imagen CLUT</v>
+        <v>Curvas de salida</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Imagen de gama</v>
+        <v>Imagen CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Cromaticidad</v>
+        <v>Imagen de gama</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Gráfico de dispersión</v>
+        <v>Cromaticidad</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Curva de respuesta tonal</v>
+        <v>Gráfico de dispersión</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Tabla de la curva</v>
+        <v>Curva de respuesta tonal</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tablas</v>
+        <v>Tabla de la curva</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Datos</v>
+        <v>Tablas</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Evaluar</v>
+        <v>Datos</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Cargando…</v>
+        <v>Evaluar</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Entrada</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Salida</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Coma flotante</v>
+        <v>Salida</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Punto de cuadrícula</v>
+        <v>Coma flotante</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalizado</v>
+        <v>Punto de cuadrícula</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Legible</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legible</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Sin cuadrícula CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Cargando…</v>
+        <v>Sin cuadrícula CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
+        <v>Cargando…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL de perfil no válida:</v>
+        <v>Neutro = dentro de la gama · rojo = fuera de la gama</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>No se pudo obtener el perfil desde</v>
+        <v>URL de perfil no válida:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
+        <v>No se pudo obtener el perfil desde</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Cargando el informe de Profile Assessment WG…</v>
+        <v>¿Cargar un perfil ICC desde este sitio externo?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
+        <v>Cargando el informe de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Informe de Profile Assessment WG</v>
+        <v>Ejecutando las comprobaciones de Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Seguridad</v>
+        <v>Informe de Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformidad</v>
+        <v>Seguridad</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Calidad</v>
+        <v>Conformidad</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>INFORME</v>
+        <v>Calidad</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>Correo electrónico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>(opcional)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>Cancelar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>Suscribirse</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>Cerrar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>Error:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Es.xlsx
+++ b/translations/Eng-Es.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3475,26 +3475,26 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Perfil HDR en la cadena</v>
+        <v>Perfil HDR ColorSpace en la cadena</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Las transformaciones a través de un perfil HDR usan su AToB0Tag — la representación SDR fijada que exige la cláusula 8.10.6 — porque la cláusula 8.10.1 no le deja etiquetas TRC. El resultado es ese respaldo, no comportamiento HDR.</v>
+        <v>Las transformaciones a través de un perfil HDR ColorSpace usan su AToB0Tag — la representación SDR fijada que exige la cláusula 8.7.1.5 — porque un perfil ColorSpace no tiene etiquetas TRC. El resultado es ese respaldo, no comportamiento HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Son perfiles HDR, sin etiquetas TRC, por lo que el gamut se construye a partir del AToB0Tag: la representación SDR fijada que la cláusula 8.10.6 exige a los consumidores sin procesamiento HDR. No es el gamut HDR del perfil, que no puede dibujarse en un PCS acotado.</v>
+        <v>Son perfiles HDR, sin etiquetas TRC, por lo que el gamut se construye a partir del AToB0Tag: la representación SDR fijada que la cláusula 8.7.1.5 exige a los consumidores sin procesamiento HDR. No es el gamut HDR del perfil, que no puede dibujarse en un PCS acotado.</v>
       </c>
     </row>
     <row r="387">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Archivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>Archivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.7.1.2 a)</v>
       </c>
     </row>
     <row r="532">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Auto (orden de la cláusula 8.10.3)</v>
+        <v>Auto (orden de la cláusula 8.7.1.3)</v>
       </c>
     </row>
     <row r="540">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Perfiles HDR</v>
+        <v>Perfiles HDR ColorSpace</v>
       </c>
     </row>
     <row r="548">
@@ -4803,1263 +4803,1271 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Perfiles HDR — transferencia lineal</v>
+        <v>Perfiles HDR ColorSpace — transferencia lineal</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>Perfiles HDR — transferencia PQ / HLG</v>
+        <v>Perfiles HDR ColorSpace — transferencia PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR con transferencia lineal.</v>
+        <v>{format} contiene luz lineal, así que solo se pueden asignar perfiles HDR ColorSpace con transferencia lineal.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR › Transferencia no lineal.</v>
+        <v>{n} perfil(es) HDR PQ/HLG del pool no se ofrecen — el panel Perfiles los lista en Perfiles HDR ColorSpace › Transferencia no lineal.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>Todavía no hay ningún perfil HDR con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR por transferencia.</v>
+        <v>Todavía no hay ningún perfil HDR ColorSpace con transferencia lineal en el pool; el panel Perfiles agrupa los perfiles HDR ColorSpace por transferencia.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.10.3).</v>
+        <v>Primarios no especificados: sin ruta HDR en esta versión</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>Margen de la pantalla</v>
+        <v>IccProfLib no aplica esta curva de ganancia: {why}. Un CMM recurre al siguiente descriptor de tone mapping (cláusula 8.7.1.3).</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
+        <v>Margen de la pantalla</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>Base</v>
+        <v>{n} pasos (≈{r}× el blanco de referencia)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>Vista previa a través del motor de color</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
+        <v>Vista previa a través del motor de color</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>Mapeado para {h} pasos</v>
+        <v>Tal como se creó (base {h} pasos, sin ganancia)</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
+        <v>Mapeado para {h} pasos</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>blanco de referencia</v>
+        <v>Los mismos píxeles de prueba (señal {transfer} creciente de izquierda a derecha: gris y luego R, G, B, Y, C, M) a través de la transformación HDR de IccProfLib. Ambas franjas se limitan a {r}× el blanco de referencia HDR, como las mostraría una pantalla con {h} pasos de margen: donde la franja superior se recorta plana, la curva de ganancia suaviza las altas luces.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>pico de la pantalla</v>
+        <v>blanco de referencia</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>Vista previa no disponible: {why}</v>
+        <v>pico de la pantalla</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>el motor de color no tomó la ruta HDR para este perfil</v>
+        <v>Vista previa no disponible: {why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>Ganancia en todos los márgenes</v>
+        <v>el motor de color no tomó la ruta HDR para este perfil</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
+        <v>Ganancia en todos los márgenes</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
+        <v>Ganancia aplicada a una entrada gris en cada margen de pantalla: el azul comprime, el rojo expande y el blanco la deja igual. Las líneas punteadas marcan las curvas de la etiqueta, la continua la base y la ámbar el control deslizante; la diagonal discontinua es donde la entrada alcanza el pico de la pantalla. Haz clic para mover el control.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>Margen de la pantalla (pasos)</v>
+        <v>Entrada (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Ganancia (pasos)</v>
+        <v>Margen de la pantalla (pasos)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>Curva de la etiqueta</v>
+        <v>Ganancia (pasos)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>Base</v>
+        <v>Curva de la etiqueta</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>Control</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>Entrada = pico de la pantalla</v>
+        <v>Control</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>Curvas tonales de gris por margen</v>
+        <v>Entrada = pico de la pantalla</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
+        <v>Curvas tonales de gris por margen</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
+        <v>La curva tonal de gris en cada margen que guarda la etiqueta, coloreada de bajo (azul) a alto (rojo), con la curva del control en ámbar. Ambos ejes están en pasos, así que la diagonal significa sin cambio.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} pasos</v>
+        <v>Salida (pasos respecto al blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} pasos (base)</v>
+        <v>{h} pasos</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>A {h} pasos (control)</v>
+        <v>{h} pasos (base)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
+        <v>A {h} pasos (control)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
+        <v>Curvas del tag, por margen: {list} pasos. Base {b} pasos, blanco de referencia HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
+        <v>Este margen está fuera del rango de curvas del tag, así que se usa sin cambios la curva más cercana — la biblioteca no extrapola más allá.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
+        <v>Algunas pendientes son derivadas (PCHIP), no almacenadas en el tag. Esa derivación reconstruye una cláusula SMPTE, así que la forma de esas curvas es provisional.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
+        <v>El tag pide tone mapping sobre el blanco de referencia, así que sus curvas las construye la biblioteca en lugar de leerlas del archivo (una construcción de un borrador de comité).</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
+        <v>Sin imágenes alternativas: el tag no pide tone mapping, solo limitar al volumen de color de la pantalla.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva a {h} pasos (sin ganancia)</v>
+        <v>Las dos curvas mezcladas en este margen combinan los canales de forma distinta, así que no hay una única curva de ganancia que dibujar. La curva tonal de abajo sigue siendo exacta.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>Curva a {h} pasos</v>
+        <v>Curva a {h} pasos (sin ganancia)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Aplicado a {h} pasos</v>
+        <v>Curva a {h} pasos</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>Ganancia aplicada a este margen</v>
+        <v>Aplicado a {h} pasos</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
+        <v>Ganancia aplicada a este margen</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>Ganancia (pasos log2)</v>
+        <v>Entrada mezclada (lineal, 1,0 = blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>Curva tonal de grises a este margen</v>
+        <v>Ganancia (pasos log2)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>Entrada (× blanco de referencia HDR)</v>
+        <v>Curva tonal de grises a este margen</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Salida (× blanco de referencia HDR)</v>
+        <v>Entrada (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>Sin cambios</v>
+        <v>Salida (× blanco de referencia HDR)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>Pico de la pantalla a {h} pasos</v>
+        <v>Sin cambios</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>Salida a {h} pasos</v>
+        <v>Pico de la pantalla a {h} pasos</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
+        <v>Salida a {h} pasos</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>Identificar pantallas</v>
+        <v>HDR, gama y relación de píxeles se actualizan cuando la ventana pasa a una pantalla donde difieren.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
+        <v>Identificar pantallas</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>Siguiendo en qué monitor está esta ventana.</v>
+        <v>Pide permiso para saber en qué monitor está esta ventana, de modo que el panel también se actualice entre pantallas parecidas y muestre el margen HDR donde el navegador lo expone.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
+        <v>Siguiendo en qué monitor está esta ventana.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
+        <v>Se denegó el permiso para identificar pantallas. Puede cambiarse en la configuración de este sitio.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>No se pudieron identificar las pantallas.</v>
+        <v>Este navegador no puede identificar pantallas; solo se aplica la actualización automática de arriba.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>Eventos de pantalla</v>
+        <v>No se pudieron identificar las pantallas.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
+        <v>Eventos de pantalla</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>Primarios de color</v>
+        <v>Aún no hay eventos. Arrastra la ventana a otro monitor.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>Características de transferencia</v>
+        <v>Primarios de color</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferencia</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>Indicador de rango completo de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>Rango completo</v>
+        <v>Indicador de rango completo de vídeo</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>Rango reducido</v>
+        <v>Rango completo</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>no asignado por la UIT-T H.273</v>
+        <v>Rango reducido</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
+        <v>no asignado por la UIT-T H.273</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
+        <v>Los primarios 2 (Sin especificar) remiten al propio perfil: los primarios se toman de las etiquetas de colorante y no de esta etiqueta.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>INFORME</v>
+        <v>Los cuatro bytes reservados de esta etiqueta no son todos cero.</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>FALLIDO</v>
+        <v>INFORME</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>comprobaciones</v>
+        <v>FALLIDO</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
+        <v>comprobaciones</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
+        <v>Generado por iccPawgReport (iccDEV) · lista de comprobación del ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>Herramienta de perfiles ICC</v>
+        <v>Herramienta de perfiles ICC · con tecnología de IccProfLib</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>Con tecnología de {lib}</v>
+        <v>Herramienta de perfiles ICC</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>Suscribirse</v>
+        <v>Con tecnología de {lib}</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Recibir notificaciones sobre nuevas versiones</v>
+        <v>Recibir notificaciones sobre nuevas versiones de profiletool</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>Cerrar</v>
+        <v>Recibir notificaciones sobre nuevas versiones</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>Correo electrónico</v>
+        <v>Le enviaremos un correo cuando se publique una nueva versión mayor o menor de profiletool. Las versiones de parche se omiten. Su dirección se revisa manualmente antes de añadirse.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>usted@ejemplo.com</v>
+        <v>Correo electrónico</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>¿Para qué usará profiletool?</v>
+        <v>usted@ejemplo.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>(opcional)</v>
+        <v>¿Para qué usará profiletool?</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
+        <v>p. ej. evaluar perfiles ICC para calibración de prensa</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>Cancelar</v>
+        <v>Acepto recibir correos sobre las versiones de profiletool. Puedo darme de baja en cualquier momento.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>Suscribirse</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>Gracias — le contactaremos.</v>
+        <v>Suscribirse</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
+        <v>Gracias — le contactaremos.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>Cerrar</v>
+        <v>Una vez aprobado, recibirá un correo de bienvenida. Después, solo le escribiremos cuando salga una nueva versión de profiletool.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>Aviso de privacidad</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>Introduzca una dirección de correo electrónico válida.</v>
+        <v>Aviso de privacidad</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
+        <v>Introduzca una dirección de correo electrónico válida.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>Revise el formulario e inténtelo de nuevo.</v>
+        <v>Demasiadas solicitudes. Inténtelo de nuevo más tarde.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
+        <v>Revise el formulario e inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Error de red. Inténtelo de nuevo.</v>
+        <v>No se pudo enviar su solicitud. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>Error:</v>
+        <v>Error de red. Inténtelo de nuevo.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>Convertir a XML</v>
+        <v>Error:</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>Convertir a JSON</v>
+        <v>Convertir a XML</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>Convertir a ICC</v>
+        <v>Convertir a JSON</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>Convirtiendo a XML…</v>
+        <v>Convertir a ICC</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>Convirtiendo a JSON…</v>
+        <v>Convirtiendo a XML…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>Convirtiendo a ICC…</v>
+        <v>Convirtiendo a JSON…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>Cargar perfil ICC</v>
+        <v>Convirtiendo a ICC…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>Zona de soltado para archivos de perfil ICC</v>
+        <v>Cargar perfil ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>ID del perfil</v>
+        <v>Zona de soltado para archivos de perfil ICC</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>No se encontraron etiquetas.</v>
+        <v>ID del perfil</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>Nombre de etiqueta</v>
+        <v>No se encontraron etiquetas.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>Nombre de etiqueta</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>Desplazamiento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>Tamaño</v>
+        <v>Desplazamiento</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>Relleno</v>
+        <v>Tamaño</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>Bytes modificados desde la carga</v>
+        <v>Relleno</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>Tipo</v>
+        <v>Bytes modificados desde la carga</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>(Sin contenido)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>bytes</v>
+        <v>(Sin contenido)</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>Cargando descripción completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>No se pudo cargar la descripción completa:</v>
+        <v>Cargando descripción completa…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
+        <v>No se pudo cargar la descripción completa:</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
+        <v>Este perfil no se pudo analizar por completo y no debe aplicarse. El encabezado y el directorio de etiquetas siguientes se muestran solo para inspección.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>Sin salida de validación</v>
+        <v>Contenido de la etiqueta no disponible — el perfil no se pudo analizar por completo.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>El perfil es válido</v>
+        <v>Sin salida de validación</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>El perfil tiene advertencias</v>
+        <v>El perfil es válido</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>El perfil no es conforme</v>
+        <v>El perfil tiene advertencias</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>Error de validación crítico</v>
+        <v>El perfil no es conforme</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>Estado de validación desconocido</v>
+        <v>Error de validación crítico</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>Crítico — mostrado solo para inspección</v>
+        <v>Estado de validación desconocido</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>No se encontraron advertencias ni errores.</v>
+        <v>Crítico — mostrado solo para inspección</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>Válido</v>
+        <v>No se encontraron advertencias ni errores.</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>Advertencia</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>Error</v>
+        <v>Advertencia</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>Desconocido</v>
+        <v>Error</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>Aprobado</v>
+        <v>Desconocido</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>Fallido</v>
+        <v>Aprobado</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>Ver en contexto</v>
+        <v>Fallido</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>Detalle de validación</v>
+        <v>Ver en contexto</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>Activado por</v>
+        <v>Detalle de validación</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>Campo</v>
+        <v>Activado por</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>Valor actual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>Requerido: 0</v>
+        <v>Valor actual</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>Esperado: {value}</v>
+        <v>Requerido: 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>No válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>Este resultado no se pudo asociar a un campo específico.</v>
+        <v>No válido</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>Cerrar</v>
+        <v>Este resultado no se pudo asociar a un campo específico.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>Cargando editor XML…</v>
+        <v>Cerrar</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Cargando editor JSON…</v>
+        <v>Cargando editor XML…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Cargando editor JSON…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
+        <v>Tiene ediciones XML sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● ediciones XML sin guardar</v>
+        <v>Tiene ediciones JSON sin guardar. ¿Sobrescribirlas con una nueva conversión desde el perfil ICC?</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● ediciones JSON sin guardar</v>
+        <v>● ediciones XML sin guardar</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● ediciones JSON sin guardar</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Haga clic en &lt;em&gt;Convertir a XML&lt;/em&gt; para generar una representación XML editable de este perfil. El XML se produce con la misma ruta de código IccLibXML que usa la herramienta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>sangría</v>
+        <v>Haga clic en &lt;em&gt;Convertir a JSON&lt;/em&gt; para generar una representación JSON editable de este perfil. El JSON se produce con la misma ruta de código IccLibJSON que usa la herramienta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>ordenar claves</v>
+        <v>sangría</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>ordenar claves</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>Perfil escrito a partir de las ediciones, pero la revalidación falló:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B707"/>
   </ignoredErrors>
 </worksheet>
 </file>